--- a/OtherAnalyses/SKOV3/data/FACSdata_clean.xlsx
+++ b/OtherAnalyses/SKOV3/data/FACSdata_clean.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leander\Documents\Statistical_Analyses\2023\NeleF_Mgat5_Skov3_CellCounts\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Leander\Documents\Papers_manuscripts\MGAT5\MGAT5KO_CART_manuscript\OtherAnalyses\SKOV3\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{537DC072-F451-4BDC-9D8D-D1D510C48F93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46F7DDE-BB40-4646-81C3-F6B5ECDDA673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14280" yWindow="-21600" windowWidth="25800" windowHeight="21000" xr2:uid="{64E1C458-DF6D-4E19-829A-24A657AEFA97}"/>
+    <workbookView xWindow="3015" yWindow="-13185" windowWidth="22830" windowHeight="12135" xr2:uid="{64E1C458-DF6D-4E19-829A-24A657AEFA97}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2067" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2065" uniqueCount="19">
   <si>
     <t>None</t>
   </si>
@@ -96,12 +96,6 @@
   </si>
   <si>
     <t>Blood</t>
-  </si>
-  <si>
-    <t>ID</t>
-  </si>
-  <si>
-    <t>No</t>
   </si>
 </sst>
 </file>
@@ -463,7 +457,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3BA01F3C-E680-46D2-8050-8083AF7ADE12}">
-  <dimension ref="A1:G516"/>
+  <dimension ref="A1:E516"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.28515625" bestFit="1" customWidth="1"/>
@@ -473,7 +467,7 @@
     <col min="5" max="5" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -489,14 +483,8 @@
       <c r="E1" t="s">
         <v>9</v>
       </c>
-      <c r="F1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>12</v>
       </c>
@@ -512,15 +500,8 @@
       <c r="E2" t="s">
         <v>18</v>
       </c>
-      <c r="F2">
-        <v>1</v>
-      </c>
-      <c r="G2" t="str">
-        <f>_xlfn.CONCAT("E30M",F2)</f>
-        <v>E30M1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -536,15 +517,8 @@
       <c r="E3" t="s">
         <v>18</v>
       </c>
-      <c r="F3">
-        <v>2</v>
-      </c>
-      <c r="G3" t="str">
-        <f t="shared" ref="G3:G66" si="0">_xlfn.CONCAT("E30M",F3)</f>
-        <v>E30M2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -560,15 +534,8 @@
       <c r="E4" t="s">
         <v>18</v>
       </c>
-      <c r="F4">
-        <v>3</v>
-      </c>
-      <c r="G4" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
@@ -584,15 +551,8 @@
       <c r="E5" t="s">
         <v>18</v>
       </c>
-      <c r="F5">
-        <v>4</v>
-      </c>
-      <c r="G5" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -608,15 +568,8 @@
       <c r="E6" t="s">
         <v>18</v>
       </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
-      <c r="G6" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -632,15 +585,8 @@
       <c r="E7" t="s">
         <v>18</v>
       </c>
-      <c r="F7">
-        <v>6</v>
-      </c>
-      <c r="G7" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -656,15 +602,8 @@
       <c r="E8" t="s">
         <v>18</v>
       </c>
-      <c r="F8">
-        <v>7</v>
-      </c>
-      <c r="G8" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -680,15 +619,8 @@
       <c r="E9" t="s">
         <v>18</v>
       </c>
-      <c r="F9">
-        <v>8</v>
-      </c>
-      <c r="G9" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -704,15 +636,8 @@
       <c r="E10" t="s">
         <v>18</v>
       </c>
-      <c r="F10">
-        <v>9</v>
-      </c>
-      <c r="G10" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M9</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -728,15 +653,8 @@
       <c r="E11" t="s">
         <v>18</v>
       </c>
-      <c r="F11">
-        <v>10</v>
-      </c>
-      <c r="G11" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -752,15 +670,8 @@
       <c r="E12" t="s">
         <v>18</v>
       </c>
-      <c r="F12">
-        <v>11</v>
-      </c>
-      <c r="G12" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M11</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>12</v>
       </c>
@@ -773,15 +684,8 @@
       <c r="E13" t="s">
         <v>18</v>
       </c>
-      <c r="F13">
-        <v>12</v>
-      </c>
-      <c r="G13" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M12</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>12</v>
       </c>
@@ -797,15 +701,8 @@
       <c r="E14" t="s">
         <v>18</v>
       </c>
-      <c r="F14">
-        <v>13</v>
-      </c>
-      <c r="G14" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -821,15 +718,8 @@
       <c r="E15" t="s">
         <v>18</v>
       </c>
-      <c r="F15">
-        <v>14</v>
-      </c>
-      <c r="G15" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>12</v>
       </c>
@@ -845,15 +735,8 @@
       <c r="E16" t="s">
         <v>18</v>
       </c>
-      <c r="F16">
-        <v>15</v>
-      </c>
-      <c r="G16" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M15</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>12</v>
       </c>
@@ -869,15 +752,8 @@
       <c r="E17" t="s">
         <v>18</v>
       </c>
-      <c r="F17">
-        <v>16</v>
-      </c>
-      <c r="G17" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>12</v>
       </c>
@@ -893,15 +769,8 @@
       <c r="E18" t="s">
         <v>18</v>
       </c>
-      <c r="F18">
-        <v>17</v>
-      </c>
-      <c r="G18" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>12</v>
       </c>
@@ -914,15 +783,8 @@
       <c r="E19" t="s">
         <v>18</v>
       </c>
-      <c r="F19">
-        <v>18</v>
-      </c>
-      <c r="G19" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M18</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>12</v>
       </c>
@@ -938,15 +800,8 @@
       <c r="E20" t="s">
         <v>18</v>
       </c>
-      <c r="F20">
-        <v>19</v>
-      </c>
-      <c r="G20" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>12</v>
       </c>
@@ -962,15 +817,8 @@
       <c r="E21" t="s">
         <v>18</v>
       </c>
-      <c r="F21">
-        <v>20</v>
-      </c>
-      <c r="G21" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>12</v>
       </c>
@@ -986,15 +834,8 @@
       <c r="E22" t="s">
         <v>18</v>
       </c>
-      <c r="F22">
-        <v>21</v>
-      </c>
-      <c r="G22" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M21</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>12</v>
       </c>
@@ -1010,15 +851,8 @@
       <c r="E23" t="s">
         <v>18</v>
       </c>
-      <c r="F23">
-        <v>22</v>
-      </c>
-      <c r="G23" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M22</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>12</v>
       </c>
@@ -1034,15 +868,8 @@
       <c r="E24" t="s">
         <v>18</v>
       </c>
-      <c r="F24">
-        <v>23</v>
-      </c>
-      <c r="G24" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M23</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -1058,15 +885,8 @@
       <c r="E25" t="s">
         <v>18</v>
       </c>
-      <c r="F25">
-        <v>24</v>
-      </c>
-      <c r="G25" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>12</v>
       </c>
@@ -1082,15 +902,8 @@
       <c r="E26" t="s">
         <v>11</v>
       </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M1</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>12</v>
       </c>
@@ -1106,15 +919,8 @@
       <c r="E27" t="s">
         <v>11</v>
       </c>
-      <c r="F27">
-        <v>2</v>
-      </c>
-      <c r="G27" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>12</v>
       </c>
@@ -1130,15 +936,8 @@
       <c r="E28" t="s">
         <v>11</v>
       </c>
-      <c r="F28">
-        <v>3</v>
-      </c>
-      <c r="G28" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M3</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>12</v>
       </c>
@@ -1154,15 +953,8 @@
       <c r="E29" t="s">
         <v>11</v>
       </c>
-      <c r="F29">
-        <v>4</v>
-      </c>
-      <c r="G29" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M4</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>12</v>
       </c>
@@ -1178,15 +970,8 @@
       <c r="E30" t="s">
         <v>11</v>
       </c>
-      <c r="F30">
-        <v>5</v>
-      </c>
-      <c r="G30" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M5</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>12</v>
       </c>
@@ -1202,15 +987,8 @@
       <c r="E31" t="s">
         <v>11</v>
       </c>
-      <c r="F31">
-        <v>6</v>
-      </c>
-      <c r="G31" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>12</v>
       </c>
@@ -1226,15 +1004,8 @@
       <c r="E32" t="s">
         <v>11</v>
       </c>
-      <c r="F32">
-        <v>7</v>
-      </c>
-      <c r="G32" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>12</v>
       </c>
@@ -1250,15 +1021,8 @@
       <c r="E33" t="s">
         <v>11</v>
       </c>
-      <c r="F33">
-        <v>8</v>
-      </c>
-      <c r="G33" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M8</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>12</v>
       </c>
@@ -1274,15 +1038,8 @@
       <c r="E34" t="s">
         <v>11</v>
       </c>
-      <c r="F34">
-        <v>9</v>
-      </c>
-      <c r="G34" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>12</v>
       </c>
@@ -1298,15 +1055,8 @@
       <c r="E35" t="s">
         <v>11</v>
       </c>
-      <c r="F35">
-        <v>10</v>
-      </c>
-      <c r="G35" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M10</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>12</v>
       </c>
@@ -1322,15 +1072,8 @@
       <c r="E36" t="s">
         <v>11</v>
       </c>
-      <c r="F36">
-        <v>11</v>
-      </c>
-      <c r="G36" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M11</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>12</v>
       </c>
@@ -1343,15 +1086,8 @@
       <c r="E37" t="s">
         <v>11</v>
       </c>
-      <c r="F37">
-        <v>12</v>
-      </c>
-      <c r="G37" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M12</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>12</v>
       </c>
@@ -1367,15 +1103,8 @@
       <c r="E38" t="s">
         <v>11</v>
       </c>
-      <c r="F38">
-        <v>13</v>
-      </c>
-      <c r="G38" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M13</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>12</v>
       </c>
@@ -1391,15 +1120,8 @@
       <c r="E39" t="s">
         <v>11</v>
       </c>
-      <c r="F39">
-        <v>14</v>
-      </c>
-      <c r="G39" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M14</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>12</v>
       </c>
@@ -1415,15 +1137,8 @@
       <c r="E40" t="s">
         <v>11</v>
       </c>
-      <c r="F40">
-        <v>15</v>
-      </c>
-      <c r="G40" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M15</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>12</v>
       </c>
@@ -1439,15 +1154,8 @@
       <c r="E41" t="s">
         <v>11</v>
       </c>
-      <c r="F41">
-        <v>16</v>
-      </c>
-      <c r="G41" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M16</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>12</v>
       </c>
@@ -1463,15 +1171,8 @@
       <c r="E42" t="s">
         <v>11</v>
       </c>
-      <c r="F42">
-        <v>17</v>
-      </c>
-      <c r="G42" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M17</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>12</v>
       </c>
@@ -1484,15 +1185,8 @@
       <c r="E43" t="s">
         <v>11</v>
       </c>
-      <c r="F43">
-        <v>18</v>
-      </c>
-      <c r="G43" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M18</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>12</v>
       </c>
@@ -1508,15 +1202,8 @@
       <c r="E44" t="s">
         <v>11</v>
       </c>
-      <c r="F44">
-        <v>19</v>
-      </c>
-      <c r="G44" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M19</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>12</v>
       </c>
@@ -1532,15 +1219,8 @@
       <c r="E45" t="s">
         <v>11</v>
       </c>
-      <c r="F45">
-        <v>20</v>
-      </c>
-      <c r="G45" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M20</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>12</v>
       </c>
@@ -1556,15 +1236,8 @@
       <c r="E46" t="s">
         <v>11</v>
       </c>
-      <c r="F46">
-        <v>21</v>
-      </c>
-      <c r="G46" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M21</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>12</v>
       </c>
@@ -1580,15 +1253,8 @@
       <c r="E47" t="s">
         <v>11</v>
       </c>
-      <c r="F47">
-        <v>22</v>
-      </c>
-      <c r="G47" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M22</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>12</v>
       </c>
@@ -1604,15 +1270,8 @@
       <c r="E48" t="s">
         <v>11</v>
       </c>
-      <c r="F48">
-        <v>23</v>
-      </c>
-      <c r="G48" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M23</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>12</v>
       </c>
@@ -1628,15 +1287,8 @@
       <c r="E49" t="s">
         <v>11</v>
       </c>
-      <c r="F49">
-        <v>24</v>
-      </c>
-      <c r="G49" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M24</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>12</v>
       </c>
@@ -1649,15 +1301,8 @@
       <c r="E50" t="s">
         <v>18</v>
       </c>
-      <c r="F50">
-        <v>1</v>
-      </c>
-      <c r="G50" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M1</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>12</v>
       </c>
@@ -1670,15 +1315,8 @@
       <c r="E51" t="s">
         <v>18</v>
       </c>
-      <c r="F51">
-        <v>2</v>
-      </c>
-      <c r="G51" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M2</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>12</v>
       </c>
@@ -1691,15 +1329,8 @@
       <c r="E52" t="s">
         <v>18</v>
       </c>
-      <c r="F52">
-        <v>3</v>
-      </c>
-      <c r="G52" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M3</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>12</v>
       </c>
@@ -1712,15 +1343,8 @@
       <c r="E53" t="s">
         <v>18</v>
       </c>
-      <c r="F53">
-        <v>4</v>
-      </c>
-      <c r="G53" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M4</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>12</v>
       </c>
@@ -1733,15 +1357,8 @@
       <c r="E54" t="s">
         <v>18</v>
       </c>
-      <c r="F54">
-        <v>5</v>
-      </c>
-      <c r="G54" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M5</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>12</v>
       </c>
@@ -1754,15 +1371,8 @@
       <c r="E55" t="s">
         <v>18</v>
       </c>
-      <c r="F55">
-        <v>6</v>
-      </c>
-      <c r="G55" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M6</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>12</v>
       </c>
@@ -1775,15 +1385,8 @@
       <c r="E56" t="s">
         <v>18</v>
       </c>
-      <c r="F56">
-        <v>7</v>
-      </c>
-      <c r="G56" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>12</v>
       </c>
@@ -1796,15 +1399,8 @@
       <c r="E57" t="s">
         <v>18</v>
       </c>
-      <c r="F57">
-        <v>8</v>
-      </c>
-      <c r="G57" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M8</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>12</v>
       </c>
@@ -1817,15 +1413,8 @@
       <c r="E58" t="s">
         <v>18</v>
       </c>
-      <c r="F58">
-        <v>9</v>
-      </c>
-      <c r="G58" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M9</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>12</v>
       </c>
@@ -1838,15 +1427,8 @@
       <c r="E59" t="s">
         <v>18</v>
       </c>
-      <c r="F59">
-        <v>10</v>
-      </c>
-      <c r="G59" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M10</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>12</v>
       </c>
@@ -1859,15 +1441,8 @@
       <c r="E60" t="s">
         <v>18</v>
       </c>
-      <c r="F60">
-        <v>11</v>
-      </c>
-      <c r="G60" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M11</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>12</v>
       </c>
@@ -1880,15 +1455,8 @@
       <c r="E61" t="s">
         <v>18</v>
       </c>
-      <c r="F61">
-        <v>12</v>
-      </c>
-      <c r="G61" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M12</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>12</v>
       </c>
@@ -1904,15 +1472,8 @@
       <c r="E62" t="s">
         <v>18</v>
       </c>
-      <c r="F62">
-        <v>13</v>
-      </c>
-      <c r="G62" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M13</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>12</v>
       </c>
@@ -1928,15 +1489,8 @@
       <c r="E63" t="s">
         <v>18</v>
       </c>
-      <c r="F63">
-        <v>14</v>
-      </c>
-      <c r="G63" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M14</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>12</v>
       </c>
@@ -1952,15 +1506,8 @@
       <c r="E64" t="s">
         <v>18</v>
       </c>
-      <c r="F64">
-        <v>15</v>
-      </c>
-      <c r="G64" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M15</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>12</v>
       </c>
@@ -1976,15 +1523,8 @@
       <c r="E65" t="s">
         <v>18</v>
       </c>
-      <c r="F65">
-        <v>16</v>
-      </c>
-      <c r="G65" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M16</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>12</v>
       </c>
@@ -2000,15 +1540,8 @@
       <c r="E66" t="s">
         <v>18</v>
       </c>
-      <c r="F66">
-        <v>17</v>
-      </c>
-      <c r="G66" t="str">
-        <f t="shared" si="0"/>
-        <v>E30M17</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>12</v>
       </c>
@@ -2021,15 +1554,8 @@
       <c r="E67" t="s">
         <v>18</v>
       </c>
-      <c r="F67">
-        <v>18</v>
-      </c>
-      <c r="G67" t="str">
-        <f t="shared" ref="G67:G121" si="1">_xlfn.CONCAT("E30M",F67)</f>
-        <v>E30M18</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>12</v>
       </c>
@@ -2045,15 +1571,8 @@
       <c r="E68" t="s">
         <v>18</v>
       </c>
-      <c r="F68">
-        <v>19</v>
-      </c>
-      <c r="G68" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M19</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>12</v>
       </c>
@@ -2069,15 +1588,8 @@
       <c r="E69" t="s">
         <v>18</v>
       </c>
-      <c r="F69">
-        <v>20</v>
-      </c>
-      <c r="G69" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M20</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>12</v>
       </c>
@@ -2093,15 +1605,8 @@
       <c r="E70" t="s">
         <v>18</v>
       </c>
-      <c r="F70">
-        <v>21</v>
-      </c>
-      <c r="G70" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M21</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>12</v>
       </c>
@@ -2117,15 +1622,8 @@
       <c r="E71" t="s">
         <v>18</v>
       </c>
-      <c r="F71">
-        <v>22</v>
-      </c>
-      <c r="G71" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M22</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>12</v>
       </c>
@@ -2141,15 +1639,8 @@
       <c r="E72" t="s">
         <v>18</v>
       </c>
-      <c r="F72">
-        <v>23</v>
-      </c>
-      <c r="G72" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M23</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>12</v>
       </c>
@@ -2162,15 +1653,8 @@
       <c r="E73" t="s">
         <v>18</v>
       </c>
-      <c r="F73">
-        <v>24</v>
-      </c>
-      <c r="G73" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M24</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>12</v>
       </c>
@@ -2186,15 +1670,8 @@
       <c r="E74" t="s">
         <v>18</v>
       </c>
-      <c r="F74">
-        <v>25</v>
-      </c>
-      <c r="G74" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M25</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>12</v>
       </c>
@@ -2210,15 +1687,8 @@
       <c r="E75" t="s">
         <v>18</v>
       </c>
-      <c r="F75">
-        <v>26</v>
-      </c>
-      <c r="G75" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M26</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>12</v>
       </c>
@@ -2234,15 +1704,8 @@
       <c r="E76" t="s">
         <v>18</v>
       </c>
-      <c r="F76">
-        <v>27</v>
-      </c>
-      <c r="G76" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M27</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>12</v>
       </c>
@@ -2258,15 +1721,8 @@
       <c r="E77" t="s">
         <v>18</v>
       </c>
-      <c r="F77">
-        <v>28</v>
-      </c>
-      <c r="G77" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M28</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>12</v>
       </c>
@@ -2282,15 +1738,8 @@
       <c r="E78" t="s">
         <v>18</v>
       </c>
-      <c r="F78">
-        <v>29</v>
-      </c>
-      <c r="G78" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M29</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>12</v>
       </c>
@@ -2306,15 +1755,8 @@
       <c r="E79" t="s">
         <v>18</v>
       </c>
-      <c r="F79">
-        <v>30</v>
-      </c>
-      <c r="G79" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M30</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>12</v>
       </c>
@@ -2330,15 +1772,8 @@
       <c r="E80" t="s">
         <v>18</v>
       </c>
-      <c r="F80">
-        <v>31</v>
-      </c>
-      <c r="G80" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M31</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>12</v>
       </c>
@@ -2354,15 +1789,8 @@
       <c r="E81" t="s">
         <v>18</v>
       </c>
-      <c r="F81">
-        <v>32</v>
-      </c>
-      <c r="G81" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M32</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>12</v>
       </c>
@@ -2375,15 +1803,8 @@
       <c r="E82" t="s">
         <v>18</v>
       </c>
-      <c r="F82">
-        <v>33</v>
-      </c>
-      <c r="G82" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M33</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>12</v>
       </c>
@@ -2396,15 +1817,8 @@
       <c r="E83" t="s">
         <v>18</v>
       </c>
-      <c r="F83">
-        <v>34</v>
-      </c>
-      <c r="G83" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M34</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>12</v>
       </c>
@@ -2417,15 +1831,8 @@
       <c r="E84" t="s">
         <v>18</v>
       </c>
-      <c r="F84">
-        <v>35</v>
-      </c>
-      <c r="G84" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M35</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>12</v>
       </c>
@@ -2438,15 +1845,8 @@
       <c r="E85" t="s">
         <v>18</v>
       </c>
-      <c r="F85">
-        <v>36</v>
-      </c>
-      <c r="G85" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M36</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>12</v>
       </c>
@@ -2459,15 +1859,8 @@
       <c r="E86" t="s">
         <v>18</v>
       </c>
-      <c r="F86">
-        <v>37</v>
-      </c>
-      <c r="G86" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M37</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>12</v>
       </c>
@@ -2483,15 +1876,8 @@
       <c r="E87" t="s">
         <v>18</v>
       </c>
-      <c r="F87">
-        <v>13</v>
-      </c>
-      <c r="G87" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M13</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>12</v>
       </c>
@@ -2507,15 +1893,8 @@
       <c r="E88" t="s">
         <v>18</v>
       </c>
-      <c r="F88">
-        <v>14</v>
-      </c>
-      <c r="G88" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M14</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>12</v>
       </c>
@@ -2531,15 +1910,8 @@
       <c r="E89" t="s">
         <v>18</v>
       </c>
-      <c r="F89">
-        <v>15</v>
-      </c>
-      <c r="G89" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M15</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>12</v>
       </c>
@@ -2555,15 +1927,8 @@
       <c r="E90" t="s">
         <v>18</v>
       </c>
-      <c r="F90">
-        <v>16</v>
-      </c>
-      <c r="G90" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M16</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>12</v>
       </c>
@@ -2579,15 +1944,8 @@
       <c r="E91" t="s">
         <v>18</v>
       </c>
-      <c r="F91">
-        <v>17</v>
-      </c>
-      <c r="G91" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M17</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>12</v>
       </c>
@@ -2600,15 +1958,8 @@
       <c r="E92" t="s">
         <v>18</v>
       </c>
-      <c r="F92">
-        <v>18</v>
-      </c>
-      <c r="G92" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M18</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>12</v>
       </c>
@@ -2624,15 +1975,8 @@
       <c r="E93" t="s">
         <v>18</v>
       </c>
-      <c r="F93">
-        <v>19</v>
-      </c>
-      <c r="G93" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M19</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>12</v>
       </c>
@@ -2648,15 +1992,8 @@
       <c r="E94" t="s">
         <v>18</v>
       </c>
-      <c r="F94">
-        <v>20</v>
-      </c>
-      <c r="G94" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M20</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>12</v>
       </c>
@@ -2672,15 +2009,8 @@
       <c r="E95" t="s">
         <v>18</v>
       </c>
-      <c r="F95">
-        <v>21</v>
-      </c>
-      <c r="G95" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M21</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>12</v>
       </c>
@@ -2696,15 +2026,8 @@
       <c r="E96" t="s">
         <v>18</v>
       </c>
-      <c r="F96">
-        <v>22</v>
-      </c>
-      <c r="G96" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M22</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>12</v>
       </c>
@@ -2720,15 +2043,8 @@
       <c r="E97" t="s">
         <v>18</v>
       </c>
-      <c r="F97">
-        <v>23</v>
-      </c>
-      <c r="G97" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M23</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>12</v>
       </c>
@@ -2744,15 +2060,8 @@
       <c r="E98" t="s">
         <v>11</v>
       </c>
-      <c r="F98">
-        <v>25</v>
-      </c>
-      <c r="G98" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M25</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>12</v>
       </c>
@@ -2768,15 +2077,8 @@
       <c r="E99" t="s">
         <v>11</v>
       </c>
-      <c r="F99">
-        <v>26</v>
-      </c>
-      <c r="G99" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M26</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>12</v>
       </c>
@@ -2792,15 +2094,8 @@
       <c r="E100" t="s">
         <v>11</v>
       </c>
-      <c r="F100">
-        <v>27</v>
-      </c>
-      <c r="G100" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M27</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>12</v>
       </c>
@@ -2816,15 +2111,8 @@
       <c r="E101" t="s">
         <v>11</v>
       </c>
-      <c r="F101">
-        <v>28</v>
-      </c>
-      <c r="G101" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M28</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>12</v>
       </c>
@@ -2840,15 +2128,8 @@
       <c r="E102" t="s">
         <v>11</v>
       </c>
-      <c r="F102">
-        <v>29</v>
-      </c>
-      <c r="G102" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M29</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>12</v>
       </c>
@@ -2864,15 +2145,8 @@
       <c r="E103" t="s">
         <v>11</v>
       </c>
-      <c r="F103">
-        <v>30</v>
-      </c>
-      <c r="G103" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M30</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>12</v>
       </c>
@@ -2888,15 +2162,8 @@
       <c r="E104" t="s">
         <v>11</v>
       </c>
-      <c r="F104">
-        <v>31</v>
-      </c>
-      <c r="G104" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M31</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>12</v>
       </c>
@@ -2912,15 +2179,8 @@
       <c r="E105" t="s">
         <v>11</v>
       </c>
-      <c r="F105">
-        <v>32</v>
-      </c>
-      <c r="G105" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M32</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>12</v>
       </c>
@@ -2933,15 +2193,8 @@
       <c r="E106" t="s">
         <v>11</v>
       </c>
-      <c r="F106">
-        <v>33</v>
-      </c>
-      <c r="G106" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M33</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>12</v>
       </c>
@@ -2954,15 +2207,8 @@
       <c r="E107" t="s">
         <v>11</v>
       </c>
-      <c r="F107">
-        <v>34</v>
-      </c>
-      <c r="G107" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M34</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>12</v>
       </c>
@@ -2975,15 +2221,8 @@
       <c r="E108" t="s">
         <v>11</v>
       </c>
-      <c r="F108">
-        <v>35</v>
-      </c>
-      <c r="G108" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M35</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>12</v>
       </c>
@@ -2996,15 +2235,8 @@
       <c r="E109" t="s">
         <v>11</v>
       </c>
-      <c r="F109">
-        <v>36</v>
-      </c>
-      <c r="G109" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M36</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>12</v>
       </c>
@@ -3017,15 +2249,8 @@
       <c r="E110" t="s">
         <v>11</v>
       </c>
-      <c r="F110">
-        <v>37</v>
-      </c>
-      <c r="G110" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M37</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>12</v>
       </c>
@@ -3041,15 +2266,8 @@
       <c r="E111" t="s">
         <v>11</v>
       </c>
-      <c r="F111">
-        <v>13</v>
-      </c>
-      <c r="G111" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M13</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>12</v>
       </c>
@@ -3065,15 +2283,8 @@
       <c r="E112" t="s">
         <v>11</v>
       </c>
-      <c r="F112">
-        <v>14</v>
-      </c>
-      <c r="G112" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M14</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>12</v>
       </c>
@@ -3089,15 +2300,8 @@
       <c r="E113" t="s">
         <v>11</v>
       </c>
-      <c r="F113">
-        <v>15</v>
-      </c>
-      <c r="G113" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M15</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>12</v>
       </c>
@@ -3113,15 +2317,8 @@
       <c r="E114" t="s">
         <v>11</v>
       </c>
-      <c r="F114">
-        <v>16</v>
-      </c>
-      <c r="G114" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M16</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>12</v>
       </c>
@@ -3137,15 +2334,8 @@
       <c r="E115" t="s">
         <v>11</v>
       </c>
-      <c r="F115">
-        <v>17</v>
-      </c>
-      <c r="G115" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M17</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>12</v>
       </c>
@@ -3158,15 +2348,8 @@
       <c r="E116" t="s">
         <v>11</v>
       </c>
-      <c r="F116">
-        <v>18</v>
-      </c>
-      <c r="G116" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M18</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>12</v>
       </c>
@@ -3182,15 +2365,8 @@
       <c r="E117" t="s">
         <v>11</v>
       </c>
-      <c r="F117">
-        <v>19</v>
-      </c>
-      <c r="G117" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M19</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>12</v>
       </c>
@@ -3206,15 +2382,8 @@
       <c r="E118" t="s">
         <v>11</v>
       </c>
-      <c r="F118">
-        <v>20</v>
-      </c>
-      <c r="G118" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M20</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>12</v>
       </c>
@@ -3230,15 +2399,8 @@
       <c r="E119" t="s">
         <v>11</v>
       </c>
-      <c r="F119">
-        <v>21</v>
-      </c>
-      <c r="G119" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M21</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>12</v>
       </c>
@@ -3254,15 +2416,8 @@
       <c r="E120" t="s">
         <v>11</v>
       </c>
-      <c r="F120">
-        <v>22</v>
-      </c>
-      <c r="G120" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M22</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>12</v>
       </c>
@@ -3278,15 +2433,8 @@
       <c r="E121" t="s">
         <v>11</v>
       </c>
-      <c r="F121">
-        <v>23</v>
-      </c>
-      <c r="G121" t="str">
-        <f t="shared" si="1"/>
-        <v>E30M23</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>16</v>
       </c>
@@ -3302,15 +2450,8 @@
       <c r="E122" t="s">
         <v>18</v>
       </c>
-      <c r="F122">
-        <v>1</v>
-      </c>
-      <c r="G122" t="str">
-        <f>_xlfn.CONCAT("E32M",F122)</f>
-        <v>E32M1</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>16</v>
       </c>
@@ -3326,15 +2467,8 @@
       <c r="E123" t="s">
         <v>18</v>
       </c>
-      <c r="F123">
-        <v>2</v>
-      </c>
-      <c r="G123" t="str">
-        <f t="shared" ref="G123:G186" si="2">_xlfn.CONCAT("E32M",F123)</f>
-        <v>E32M2</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>16</v>
       </c>
@@ -3350,15 +2484,8 @@
       <c r="E124" t="s">
         <v>18</v>
       </c>
-      <c r="F124">
-        <v>3</v>
-      </c>
-      <c r="G124" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M3</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>16</v>
       </c>
@@ -3374,15 +2501,8 @@
       <c r="E125" t="s">
         <v>18</v>
       </c>
-      <c r="F125">
-        <v>4</v>
-      </c>
-      <c r="G125" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M4</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>16</v>
       </c>
@@ -3395,15 +2515,8 @@
       <c r="E126" t="s">
         <v>18</v>
       </c>
-      <c r="F126">
-        <v>5</v>
-      </c>
-      <c r="G126" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M5</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>16</v>
       </c>
@@ -3416,15 +2529,8 @@
       <c r="E127" t="s">
         <v>18</v>
       </c>
-      <c r="F127">
-        <v>6</v>
-      </c>
-      <c r="G127" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M6</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>16</v>
       </c>
@@ -3437,15 +2543,8 @@
       <c r="E128" t="s">
         <v>18</v>
       </c>
-      <c r="F128">
-        <v>7</v>
-      </c>
-      <c r="G128" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M7</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>16</v>
       </c>
@@ -3458,15 +2557,8 @@
       <c r="E129" t="s">
         <v>18</v>
       </c>
-      <c r="F129">
-        <v>8</v>
-      </c>
-      <c r="G129" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M8</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>16</v>
       </c>
@@ -3479,15 +2571,8 @@
       <c r="E130" t="s">
         <v>18</v>
       </c>
-      <c r="F130">
-        <v>9</v>
-      </c>
-      <c r="G130" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M9</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>16</v>
       </c>
@@ -3503,15 +2588,8 @@
       <c r="E131" t="s">
         <v>18</v>
       </c>
-      <c r="F131">
-        <v>10</v>
-      </c>
-      <c r="G131" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M10</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>16</v>
       </c>
@@ -3527,15 +2605,8 @@
       <c r="E132" t="s">
         <v>18</v>
       </c>
-      <c r="F132">
-        <v>11</v>
-      </c>
-      <c r="G132" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M11</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>16</v>
       </c>
@@ -3551,15 +2622,8 @@
       <c r="E133" t="s">
         <v>18</v>
       </c>
-      <c r="F133">
-        <v>12</v>
-      </c>
-      <c r="G133" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M12</v>
-      </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>16</v>
       </c>
@@ -3575,15 +2639,8 @@
       <c r="E134" t="s">
         <v>18</v>
       </c>
-      <c r="F134">
-        <v>13</v>
-      </c>
-      <c r="G134" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M13</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>16</v>
       </c>
@@ -3599,15 +2656,8 @@
       <c r="E135" t="s">
         <v>18</v>
       </c>
-      <c r="F135">
-        <v>14</v>
-      </c>
-      <c r="G135" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M14</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>16</v>
       </c>
@@ -3623,15 +2673,8 @@
       <c r="E136" t="s">
         <v>18</v>
       </c>
-      <c r="F136">
-        <v>15</v>
-      </c>
-      <c r="G136" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M15</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>16</v>
       </c>
@@ -3644,15 +2687,8 @@
       <c r="E137" t="s">
         <v>18</v>
       </c>
-      <c r="F137">
-        <v>16</v>
-      </c>
-      <c r="G137" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M16</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>16</v>
       </c>
@@ -3665,15 +2701,8 @@
       <c r="E138" t="s">
         <v>18</v>
       </c>
-      <c r="F138">
-        <v>17</v>
-      </c>
-      <c r="G138" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M17</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>16</v>
       </c>
@@ -3686,15 +2715,8 @@
       <c r="E139" t="s">
         <v>18</v>
       </c>
-      <c r="F139">
-        <v>18</v>
-      </c>
-      <c r="G139" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M18</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>16</v>
       </c>
@@ -3710,15 +2732,8 @@
       <c r="E140" t="s">
         <v>18</v>
       </c>
-      <c r="F140">
-        <v>19</v>
-      </c>
-      <c r="G140" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M19</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>16</v>
       </c>
@@ -3734,15 +2749,8 @@
       <c r="E141" t="s">
         <v>18</v>
       </c>
-      <c r="F141">
-        <v>20</v>
-      </c>
-      <c r="G141" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M20</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>16</v>
       </c>
@@ -3758,15 +2766,8 @@
       <c r="E142" t="s">
         <v>18</v>
       </c>
-      <c r="F142">
-        <v>21</v>
-      </c>
-      <c r="G142" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M21</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>16</v>
       </c>
@@ -3782,15 +2783,8 @@
       <c r="E143" t="s">
         <v>18</v>
       </c>
-      <c r="F143">
-        <v>22</v>
-      </c>
-      <c r="G143" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M22</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>16</v>
       </c>
@@ -3806,15 +2800,8 @@
       <c r="E144" t="s">
         <v>18</v>
       </c>
-      <c r="F144">
-        <v>23</v>
-      </c>
-      <c r="G144" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M23</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>16</v>
       </c>
@@ -3830,15 +2817,8 @@
       <c r="E145" t="s">
         <v>18</v>
       </c>
-      <c r="F145">
-        <v>24</v>
-      </c>
-      <c r="G145" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M24</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>16</v>
       </c>
@@ -3851,15 +2831,8 @@
       <c r="E146" t="s">
         <v>18</v>
       </c>
-      <c r="F146">
-        <v>25</v>
-      </c>
-      <c r="G146" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M25</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>16</v>
       </c>
@@ -3872,15 +2845,8 @@
       <c r="E147" t="s">
         <v>18</v>
       </c>
-      <c r="F147">
-        <v>26</v>
-      </c>
-      <c r="G147" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M26</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>16</v>
       </c>
@@ -3893,15 +2859,8 @@
       <c r="E148" t="s">
         <v>18</v>
       </c>
-      <c r="F148">
-        <v>27</v>
-      </c>
-      <c r="G148" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M27</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>16</v>
       </c>
@@ -3917,15 +2876,8 @@
       <c r="E149" t="s">
         <v>18</v>
       </c>
-      <c r="F149">
-        <v>28</v>
-      </c>
-      <c r="G149" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M28</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>16</v>
       </c>
@@ -3941,15 +2893,8 @@
       <c r="E150" t="s">
         <v>18</v>
       </c>
-      <c r="F150">
-        <v>29</v>
-      </c>
-      <c r="G150" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M29</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>16</v>
       </c>
@@ -3965,15 +2910,8 @@
       <c r="E151" t="s">
         <v>18</v>
       </c>
-      <c r="F151">
-        <v>30</v>
-      </c>
-      <c r="G151" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M30</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>16</v>
       </c>
@@ -3989,15 +2927,8 @@
       <c r="E152" t="s">
         <v>18</v>
       </c>
-      <c r="F152">
-        <v>31</v>
-      </c>
-      <c r="G152" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M31</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>16</v>
       </c>
@@ -4013,15 +2944,8 @@
       <c r="E153" t="s">
         <v>18</v>
       </c>
-      <c r="F153">
-        <v>32</v>
-      </c>
-      <c r="G153" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M32</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>16</v>
       </c>
@@ -4037,15 +2961,8 @@
       <c r="E154" t="s">
         <v>18</v>
       </c>
-      <c r="F154">
-        <v>33</v>
-      </c>
-      <c r="G154" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M33</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>16</v>
       </c>
@@ -4061,15 +2978,8 @@
       <c r="E155" t="s">
         <v>18</v>
       </c>
-      <c r="F155">
-        <v>34</v>
-      </c>
-      <c r="G155" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M34</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>16</v>
       </c>
@@ -4085,15 +2995,8 @@
       <c r="E156" t="s">
         <v>18</v>
       </c>
-      <c r="F156">
-        <v>35</v>
-      </c>
-      <c r="G156" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M35</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>16</v>
       </c>
@@ -4109,15 +3012,8 @@
       <c r="E157" t="s">
         <v>18</v>
       </c>
-      <c r="F157">
-        <v>36</v>
-      </c>
-      <c r="G157" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M36</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>16</v>
       </c>
@@ -4133,15 +3029,8 @@
       <c r="E158" t="s">
         <v>18</v>
       </c>
-      <c r="F158">
-        <v>37</v>
-      </c>
-      <c r="G158" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M37</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>16</v>
       </c>
@@ -4157,15 +3046,8 @@
       <c r="E159" t="s">
         <v>18</v>
       </c>
-      <c r="F159">
-        <v>38</v>
-      </c>
-      <c r="G159" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M38</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>16</v>
       </c>
@@ -4181,15 +3063,8 @@
       <c r="E160" t="s">
         <v>18</v>
       </c>
-      <c r="F160">
-        <v>39</v>
-      </c>
-      <c r="G160" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M39</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>16</v>
       </c>
@@ -4205,15 +3080,8 @@
       <c r="E161" t="s">
         <v>18</v>
       </c>
-      <c r="F161">
-        <v>40</v>
-      </c>
-      <c r="G161" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M40</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>16</v>
       </c>
@@ -4229,15 +3097,8 @@
       <c r="E162" t="s">
         <v>18</v>
       </c>
-      <c r="F162">
-        <v>41</v>
-      </c>
-      <c r="G162" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M41</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>16</v>
       </c>
@@ -4253,15 +3114,8 @@
       <c r="E163" t="s">
         <v>18</v>
       </c>
-      <c r="F163">
-        <v>42</v>
-      </c>
-      <c r="G163" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M42</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>16</v>
       </c>
@@ -4277,15 +3131,8 @@
       <c r="E164" t="s">
         <v>18</v>
       </c>
-      <c r="F164">
-        <v>43</v>
-      </c>
-      <c r="G164" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M43</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>16</v>
       </c>
@@ -4301,15 +3148,8 @@
       <c r="E165" t="s">
         <v>18</v>
       </c>
-      <c r="F165">
-        <v>44</v>
-      </c>
-      <c r="G165" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M44</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>16</v>
       </c>
@@ -4325,15 +3165,8 @@
       <c r="E166" t="s">
         <v>18</v>
       </c>
-      <c r="F166">
-        <v>45</v>
-      </c>
-      <c r="G166" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M45</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>16</v>
       </c>
@@ -4349,15 +3182,8 @@
       <c r="E167" t="s">
         <v>18</v>
       </c>
-      <c r="F167">
-        <v>46</v>
-      </c>
-      <c r="G167" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M46</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>16</v>
       </c>
@@ -4373,15 +3199,8 @@
       <c r="E168" t="s">
         <v>18</v>
       </c>
-      <c r="F168">
-        <v>47</v>
-      </c>
-      <c r="G168" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M47</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>16</v>
       </c>
@@ -4397,15 +3216,8 @@
       <c r="E169" t="s">
         <v>18</v>
       </c>
-      <c r="F169">
-        <v>48</v>
-      </c>
-      <c r="G169" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M48</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>16</v>
       </c>
@@ -4421,15 +3233,8 @@
       <c r="E170" t="s">
         <v>18</v>
       </c>
-      <c r="F170">
-        <v>49</v>
-      </c>
-      <c r="G170" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M49</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>16</v>
       </c>
@@ -4445,15 +3250,8 @@
       <c r="E171" t="s">
         <v>18</v>
       </c>
-      <c r="F171">
-        <v>50</v>
-      </c>
-      <c r="G171" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M50</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>16</v>
       </c>
@@ -4469,15 +3267,8 @@
       <c r="E172" t="s">
         <v>18</v>
       </c>
-      <c r="F172">
-        <v>51</v>
-      </c>
-      <c r="G172" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M51</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>16</v>
       </c>
@@ -4493,15 +3284,8 @@
       <c r="E173" t="s">
         <v>18</v>
       </c>
-      <c r="F173">
-        <v>52</v>
-      </c>
-      <c r="G173" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M52</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>16</v>
       </c>
@@ -4517,15 +3301,8 @@
       <c r="E174" t="s">
         <v>18</v>
       </c>
-      <c r="F174">
-        <v>53</v>
-      </c>
-      <c r="G174" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M53</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>16</v>
       </c>
@@ -4541,15 +3318,8 @@
       <c r="E175" t="s">
         <v>18</v>
       </c>
-      <c r="F175">
-        <v>54</v>
-      </c>
-      <c r="G175" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M54</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>16</v>
       </c>
@@ -4565,15 +3335,8 @@
       <c r="E176" t="s">
         <v>18</v>
       </c>
-      <c r="F176">
-        <v>55</v>
-      </c>
-      <c r="G176" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M55</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>16</v>
       </c>
@@ -4589,15 +3352,8 @@
       <c r="E177" t="s">
         <v>18</v>
       </c>
-      <c r="F177">
-        <v>56</v>
-      </c>
-      <c r="G177" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M56</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>16</v>
       </c>
@@ -4613,15 +3369,8 @@
       <c r="E178" t="s">
         <v>18</v>
       </c>
-      <c r="F178">
-        <v>57</v>
-      </c>
-      <c r="G178" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M57</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>16</v>
       </c>
@@ -4637,15 +3386,8 @@
       <c r="E179" t="s">
         <v>18</v>
       </c>
-      <c r="F179">
-        <v>58</v>
-      </c>
-      <c r="G179" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M58</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>16</v>
       </c>
@@ -4661,15 +3403,8 @@
       <c r="E180" t="s">
         <v>18</v>
       </c>
-      <c r="F180">
-        <v>59</v>
-      </c>
-      <c r="G180" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M59</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>16</v>
       </c>
@@ -4685,15 +3420,8 @@
       <c r="E181" t="s">
         <v>18</v>
       </c>
-      <c r="F181">
-        <v>60</v>
-      </c>
-      <c r="G181" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M60</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>16</v>
       </c>
@@ -4709,15 +3437,8 @@
       <c r="E182" t="s">
         <v>18</v>
       </c>
-      <c r="F182">
-        <v>61</v>
-      </c>
-      <c r="G182" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M61</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>16</v>
       </c>
@@ -4733,15 +3454,8 @@
       <c r="E183" t="s">
         <v>18</v>
       </c>
-      <c r="F183">
-        <v>62</v>
-      </c>
-      <c r="G183" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M62</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>16</v>
       </c>
@@ -4757,15 +3471,8 @@
       <c r="E184" t="s">
         <v>18</v>
       </c>
-      <c r="F184">
-        <v>63</v>
-      </c>
-      <c r="G184" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M63</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>16</v>
       </c>
@@ -4781,15 +3488,8 @@
       <c r="E185" t="s">
         <v>18</v>
       </c>
-      <c r="F185">
-        <v>64</v>
-      </c>
-      <c r="G185" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M64</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>16</v>
       </c>
@@ -4805,15 +3505,8 @@
       <c r="E186" t="s">
         <v>18</v>
       </c>
-      <c r="F186">
-        <v>65</v>
-      </c>
-      <c r="G186" t="str">
-        <f t="shared" si="2"/>
-        <v>E32M65</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>16</v>
       </c>
@@ -4829,15 +3522,8 @@
       <c r="E187" t="s">
         <v>18</v>
       </c>
-      <c r="F187">
-        <v>66</v>
-      </c>
-      <c r="G187" t="str">
-        <f t="shared" ref="G187:G250" si="3">_xlfn.CONCAT("E32M",F187)</f>
-        <v>E32M66</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>16</v>
       </c>
@@ -4853,15 +3539,8 @@
       <c r="E188" t="s">
         <v>18</v>
       </c>
-      <c r="F188">
-        <v>28</v>
-      </c>
-      <c r="G188" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M28</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>16</v>
       </c>
@@ -4877,15 +3556,8 @@
       <c r="E189" t="s">
         <v>18</v>
       </c>
-      <c r="F189">
-        <v>29</v>
-      </c>
-      <c r="G189" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M29</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>16</v>
       </c>
@@ -4901,15 +3573,8 @@
       <c r="E190" t="s">
         <v>18</v>
       </c>
-      <c r="F190">
-        <v>30</v>
-      </c>
-      <c r="G190" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M30</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>16</v>
       </c>
@@ -4925,15 +3590,8 @@
       <c r="E191" t="s">
         <v>18</v>
       </c>
-      <c r="F191">
-        <v>31</v>
-      </c>
-      <c r="G191" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M31</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>16</v>
       </c>
@@ -4949,15 +3607,8 @@
       <c r="E192" t="s">
         <v>18</v>
       </c>
-      <c r="F192">
-        <v>32</v>
-      </c>
-      <c r="G192" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M32</v>
-      </c>
-    </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>16</v>
       </c>
@@ -4973,15 +3624,8 @@
       <c r="E193" t="s">
         <v>18</v>
       </c>
-      <c r="F193">
-        <v>33</v>
-      </c>
-      <c r="G193" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M33</v>
-      </c>
-    </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>16</v>
       </c>
@@ -4997,15 +3641,8 @@
       <c r="E194" t="s">
         <v>18</v>
       </c>
-      <c r="F194">
-        <v>34</v>
-      </c>
-      <c r="G194" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M34</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>16</v>
       </c>
@@ -5021,15 +3658,8 @@
       <c r="E195" t="s">
         <v>18</v>
       </c>
-      <c r="F195">
-        <v>35</v>
-      </c>
-      <c r="G195" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M35</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>16</v>
       </c>
@@ -5042,15 +3672,8 @@
       <c r="E196" t="s">
         <v>18</v>
       </c>
-      <c r="F196">
-        <v>36</v>
-      </c>
-      <c r="G196" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M36</v>
-      </c>
-    </row>
-    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>16</v>
       </c>
@@ -5066,15 +3689,8 @@
       <c r="E197" t="s">
         <v>18</v>
       </c>
-      <c r="F197">
-        <v>37</v>
-      </c>
-      <c r="G197" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M37</v>
-      </c>
-    </row>
-    <row r="198" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>16</v>
       </c>
@@ -5090,15 +3706,8 @@
       <c r="E198" t="s">
         <v>18</v>
       </c>
-      <c r="F198">
-        <v>38</v>
-      </c>
-      <c r="G198" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M38</v>
-      </c>
-    </row>
-    <row r="199" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>16</v>
       </c>
@@ -5114,15 +3723,8 @@
       <c r="E199" t="s">
         <v>18</v>
       </c>
-      <c r="F199">
-        <v>39</v>
-      </c>
-      <c r="G199" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M39</v>
-      </c>
-    </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>16</v>
       </c>
@@ -5138,15 +3740,8 @@
       <c r="E200" t="s">
         <v>18</v>
       </c>
-      <c r="F200">
-        <v>40</v>
-      </c>
-      <c r="G200" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M40</v>
-      </c>
-    </row>
-    <row r="201" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>16</v>
       </c>
@@ -5162,15 +3757,8 @@
       <c r="E201" t="s">
         <v>18</v>
       </c>
-      <c r="F201">
-        <v>41</v>
-      </c>
-      <c r="G201" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M41</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>16</v>
       </c>
@@ -5183,15 +3771,8 @@
       <c r="E202" t="s">
         <v>18</v>
       </c>
-      <c r="F202">
-        <v>42</v>
-      </c>
-      <c r="G202" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M42</v>
-      </c>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>16</v>
       </c>
@@ -5204,15 +3785,8 @@
       <c r="E203" t="s">
         <v>18</v>
       </c>
-      <c r="F203">
-        <v>43</v>
-      </c>
-      <c r="G203" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M43</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>16</v>
       </c>
@@ -5225,15 +3799,8 @@
       <c r="E204" t="s">
         <v>18</v>
       </c>
-      <c r="F204">
-        <v>44</v>
-      </c>
-      <c r="G204" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M44</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>16</v>
       </c>
@@ -5246,15 +3813,8 @@
       <c r="E205" t="s">
         <v>18</v>
       </c>
-      <c r="F205">
-        <v>45</v>
-      </c>
-      <c r="G205" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M45</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>16</v>
       </c>
@@ -5270,15 +3830,8 @@
       <c r="E206" t="s">
         <v>18</v>
       </c>
-      <c r="F206">
-        <v>46</v>
-      </c>
-      <c r="G206" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M46</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>16</v>
       </c>
@@ -5294,15 +3847,8 @@
       <c r="E207" t="s">
         <v>18</v>
       </c>
-      <c r="F207">
-        <v>47</v>
-      </c>
-      <c r="G207" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M47</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>16</v>
       </c>
@@ -5318,15 +3864,8 @@
       <c r="E208" t="s">
         <v>18</v>
       </c>
-      <c r="F208">
-        <v>48</v>
-      </c>
-      <c r="G208" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M48</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>16</v>
       </c>
@@ -5342,15 +3881,8 @@
       <c r="E209" t="s">
         <v>18</v>
       </c>
-      <c r="F209">
-        <v>49</v>
-      </c>
-      <c r="G209" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M49</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>16</v>
       </c>
@@ -5366,15 +3898,8 @@
       <c r="E210" t="s">
         <v>18</v>
       </c>
-      <c r="F210">
-        <v>50</v>
-      </c>
-      <c r="G210" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M50</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>16</v>
       </c>
@@ -5390,15 +3915,8 @@
       <c r="E211" t="s">
         <v>18</v>
       </c>
-      <c r="F211">
-        <v>51</v>
-      </c>
-      <c r="G211" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M51</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>16</v>
       </c>
@@ -5414,15 +3932,8 @@
       <c r="E212" t="s">
         <v>18</v>
       </c>
-      <c r="F212">
-        <v>52</v>
-      </c>
-      <c r="G212" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M52</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>16</v>
       </c>
@@ -5438,15 +3949,8 @@
       <c r="E213" t="s">
         <v>18</v>
       </c>
-      <c r="F213">
-        <v>53</v>
-      </c>
-      <c r="G213" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M53</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>16</v>
       </c>
@@ -5462,15 +3966,8 @@
       <c r="E214" t="s">
         <v>18</v>
       </c>
-      <c r="F214">
-        <v>54</v>
-      </c>
-      <c r="G214" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M54</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>16</v>
       </c>
@@ -5483,15 +3980,8 @@
       <c r="E215" t="s">
         <v>18</v>
       </c>
-      <c r="F215">
-        <v>55</v>
-      </c>
-      <c r="G215" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M55</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>16</v>
       </c>
@@ -5507,15 +3997,8 @@
       <c r="E216" t="s">
         <v>18</v>
       </c>
-      <c r="F216">
-        <v>56</v>
-      </c>
-      <c r="G216" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M56</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="217" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>16</v>
       </c>
@@ -5531,15 +4014,8 @@
       <c r="E217" t="s">
         <v>18</v>
       </c>
-      <c r="F217">
-        <v>57</v>
-      </c>
-      <c r="G217" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M57</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>16</v>
       </c>
@@ -5555,15 +4031,8 @@
       <c r="E218" t="s">
         <v>18</v>
       </c>
-      <c r="F218">
-        <v>58</v>
-      </c>
-      <c r="G218" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M58</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="219" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>16</v>
       </c>
@@ -5579,15 +4048,8 @@
       <c r="E219" t="s">
         <v>18</v>
       </c>
-      <c r="F219">
-        <v>59</v>
-      </c>
-      <c r="G219" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M59</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>16</v>
       </c>
@@ -5600,15 +4062,8 @@
       <c r="E220" t="s">
         <v>18</v>
       </c>
-      <c r="F220">
-        <v>60</v>
-      </c>
-      <c r="G220" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M60</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>16</v>
       </c>
@@ -5624,15 +4079,8 @@
       <c r="E221" t="s">
         <v>18</v>
       </c>
-      <c r="F221">
-        <v>61</v>
-      </c>
-      <c r="G221" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M61</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>16</v>
       </c>
@@ -5648,15 +4096,8 @@
       <c r="E222" t="s">
         <v>18</v>
       </c>
-      <c r="F222">
-        <v>62</v>
-      </c>
-      <c r="G222" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M62</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>16</v>
       </c>
@@ -5672,15 +4113,8 @@
       <c r="E223" t="s">
         <v>18</v>
       </c>
-      <c r="F223">
-        <v>63</v>
-      </c>
-      <c r="G223" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M63</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>16</v>
       </c>
@@ -5696,15 +4130,8 @@
       <c r="E224" t="s">
         <v>18</v>
       </c>
-      <c r="F224">
-        <v>64</v>
-      </c>
-      <c r="G224" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M64</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>16</v>
       </c>
@@ -5717,15 +4144,8 @@
       <c r="E225" t="s">
         <v>18</v>
       </c>
-      <c r="F225">
-        <v>65</v>
-      </c>
-      <c r="G225" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M65</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="226" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>16</v>
       </c>
@@ -5741,15 +4161,8 @@
       <c r="E226" t="s">
         <v>18</v>
       </c>
-      <c r="F226">
-        <v>66</v>
-      </c>
-      <c r="G226" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M66</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="227" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>16</v>
       </c>
@@ -5765,15 +4178,8 @@
       <c r="E227" t="s">
         <v>18</v>
       </c>
-      <c r="F227">
-        <v>28</v>
-      </c>
-      <c r="G227" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M28</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>16</v>
       </c>
@@ -5789,15 +4195,8 @@
       <c r="E228" t="s">
         <v>18</v>
       </c>
-      <c r="F228">
-        <v>29</v>
-      </c>
-      <c r="G228" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M29</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>16</v>
       </c>
@@ -5813,15 +4212,8 @@
       <c r="E229" t="s">
         <v>18</v>
       </c>
-      <c r="F229">
-        <v>30</v>
-      </c>
-      <c r="G229" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M30</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>16</v>
       </c>
@@ -5837,15 +4229,8 @@
       <c r="E230" t="s">
         <v>18</v>
       </c>
-      <c r="F230">
-        <v>31</v>
-      </c>
-      <c r="G230" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M31</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="231" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>16</v>
       </c>
@@ -5861,15 +4246,8 @@
       <c r="E231" t="s">
         <v>18</v>
       </c>
-      <c r="F231">
-        <v>32</v>
-      </c>
-      <c r="G231" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M32</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>16</v>
       </c>
@@ -5885,15 +4263,8 @@
       <c r="E232" t="s">
         <v>18</v>
       </c>
-      <c r="F232">
-        <v>33</v>
-      </c>
-      <c r="G232" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M33</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>16</v>
       </c>
@@ -5909,15 +4280,8 @@
       <c r="E233" t="s">
         <v>18</v>
       </c>
-      <c r="F233">
-        <v>34</v>
-      </c>
-      <c r="G233" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M34</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>16</v>
       </c>
@@ -5930,15 +4294,8 @@
       <c r="E234" t="s">
         <v>18</v>
       </c>
-      <c r="F234">
-        <v>35</v>
-      </c>
-      <c r="G234" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M35</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>16</v>
       </c>
@@ -5951,15 +4308,8 @@
       <c r="E235" t="s">
         <v>18</v>
       </c>
-      <c r="F235">
-        <v>36</v>
-      </c>
-      <c r="G235" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M36</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>16</v>
       </c>
@@ -5975,15 +4325,8 @@
       <c r="E236" t="s">
         <v>18</v>
       </c>
-      <c r="F236">
-        <v>37</v>
-      </c>
-      <c r="G236" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M37</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="237" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A237" t="s">
         <v>16</v>
       </c>
@@ -5999,15 +4342,8 @@
       <c r="E237" t="s">
         <v>18</v>
       </c>
-      <c r="F237">
-        <v>38</v>
-      </c>
-      <c r="G237" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M38</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>16</v>
       </c>
@@ -6023,15 +4359,8 @@
       <c r="E238" t="s">
         <v>18</v>
       </c>
-      <c r="F238">
-        <v>39</v>
-      </c>
-      <c r="G238" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M39</v>
-      </c>
-    </row>
-    <row r="239" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="239" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
         <v>16</v>
       </c>
@@ -6047,15 +4376,8 @@
       <c r="E239" t="s">
         <v>18</v>
       </c>
-      <c r="F239">
-        <v>40</v>
-      </c>
-      <c r="G239" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M40</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="240" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
         <v>16</v>
       </c>
@@ -6071,15 +4393,8 @@
       <c r="E240" t="s">
         <v>18</v>
       </c>
-      <c r="F240">
-        <v>41</v>
-      </c>
-      <c r="G240" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M41</v>
-      </c>
-    </row>
-    <row r="241" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="241" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
         <v>16</v>
       </c>
@@ -6092,15 +4407,8 @@
       <c r="E241" t="s">
         <v>18</v>
       </c>
-      <c r="F241">
-        <v>42</v>
-      </c>
-      <c r="G241" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M42</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="242" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
         <v>16</v>
       </c>
@@ -6113,15 +4421,8 @@
       <c r="E242" t="s">
         <v>18</v>
       </c>
-      <c r="F242">
-        <v>43</v>
-      </c>
-      <c r="G242" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M43</v>
-      </c>
-    </row>
-    <row r="243" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="243" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A243" t="s">
         <v>16</v>
       </c>
@@ -6134,15 +4435,8 @@
       <c r="E243" t="s">
         <v>18</v>
       </c>
-      <c r="F243">
-        <v>44</v>
-      </c>
-      <c r="G243" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M44</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>16</v>
       </c>
@@ -6155,15 +4449,8 @@
       <c r="E244" t="s">
         <v>18</v>
       </c>
-      <c r="F244">
-        <v>45</v>
-      </c>
-      <c r="G244" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M45</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="245" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A245" t="s">
         <v>16</v>
       </c>
@@ -6179,15 +4466,8 @@
       <c r="E245" t="s">
         <v>18</v>
       </c>
-      <c r="F245">
-        <v>46</v>
-      </c>
-      <c r="G245" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M46</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="246" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A246" t="s">
         <v>16</v>
       </c>
@@ -6203,15 +4483,8 @@
       <c r="E246" t="s">
         <v>18</v>
       </c>
-      <c r="F246">
-        <v>47</v>
-      </c>
-      <c r="G246" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M47</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="247" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A247" t="s">
         <v>16</v>
       </c>
@@ -6227,15 +4500,8 @@
       <c r="E247" t="s">
         <v>18</v>
       </c>
-      <c r="F247">
-        <v>48</v>
-      </c>
-      <c r="G247" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M48</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="248" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A248" t="s">
         <v>16</v>
       </c>
@@ -6251,15 +4517,8 @@
       <c r="E248" t="s">
         <v>18</v>
       </c>
-      <c r="F248">
-        <v>49</v>
-      </c>
-      <c r="G248" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M49</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>16</v>
       </c>
@@ -6275,15 +4534,8 @@
       <c r="E249" t="s">
         <v>18</v>
       </c>
-      <c r="F249">
-        <v>50</v>
-      </c>
-      <c r="G249" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M50</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>16</v>
       </c>
@@ -6299,15 +4551,8 @@
       <c r="E250" t="s">
         <v>18</v>
       </c>
-      <c r="F250">
-        <v>51</v>
-      </c>
-      <c r="G250" t="str">
-        <f t="shared" si="3"/>
-        <v>E32M51</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>16</v>
       </c>
@@ -6323,15 +4568,8 @@
       <c r="E251" t="s">
         <v>18</v>
       </c>
-      <c r="F251">
-        <v>52</v>
-      </c>
-      <c r="G251" t="str">
-        <f t="shared" ref="G251:G292" si="4">_xlfn.CONCAT("E32M",F251)</f>
-        <v>E32M52</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="252" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
         <v>16</v>
       </c>
@@ -6347,15 +4585,8 @@
       <c r="E252" t="s">
         <v>18</v>
       </c>
-      <c r="F252">
-        <v>53</v>
-      </c>
-      <c r="G252" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M53</v>
-      </c>
-    </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>16</v>
       </c>
@@ -6371,15 +4602,8 @@
       <c r="E253" t="s">
         <v>18</v>
       </c>
-      <c r="F253">
-        <v>54</v>
-      </c>
-      <c r="G253" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M54</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>16</v>
       </c>
@@ -6392,15 +4616,8 @@
       <c r="E254" t="s">
         <v>11</v>
       </c>
-      <c r="F254">
-        <v>55</v>
-      </c>
-      <c r="G254" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M55</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>16</v>
       </c>
@@ -6416,15 +4633,8 @@
       <c r="E255" t="s">
         <v>11</v>
       </c>
-      <c r="F255">
-        <v>56</v>
-      </c>
-      <c r="G255" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M56</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>16</v>
       </c>
@@ -6440,15 +4650,8 @@
       <c r="E256" t="s">
         <v>11</v>
       </c>
-      <c r="F256">
-        <v>57</v>
-      </c>
-      <c r="G256" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M57</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="257" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>16</v>
       </c>
@@ -6464,15 +4667,8 @@
       <c r="E257" t="s">
         <v>11</v>
       </c>
-      <c r="F257">
-        <v>58</v>
-      </c>
-      <c r="G257" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M58</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>16</v>
       </c>
@@ -6488,15 +4684,8 @@
       <c r="E258" t="s">
         <v>11</v>
       </c>
-      <c r="F258">
-        <v>59</v>
-      </c>
-      <c r="G258" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M59</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="259" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>16</v>
       </c>
@@ -6509,15 +4698,8 @@
       <c r="E259" t="s">
         <v>11</v>
       </c>
-      <c r="F259">
-        <v>60</v>
-      </c>
-      <c r="G259" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M60</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>16</v>
       </c>
@@ -6533,15 +4715,8 @@
       <c r="E260" t="s">
         <v>11</v>
       </c>
-      <c r="F260">
-        <v>61</v>
-      </c>
-      <c r="G260" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M61</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>16</v>
       </c>
@@ -6557,15 +4732,8 @@
       <c r="E261" t="s">
         <v>11</v>
       </c>
-      <c r="F261">
-        <v>62</v>
-      </c>
-      <c r="G261" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M62</v>
-      </c>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="262" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>16</v>
       </c>
@@ -6581,15 +4749,8 @@
       <c r="E262" t="s">
         <v>11</v>
       </c>
-      <c r="F262">
-        <v>63</v>
-      </c>
-      <c r="G262" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M63</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>16</v>
       </c>
@@ -6605,15 +4766,8 @@
       <c r="E263" t="s">
         <v>11</v>
       </c>
-      <c r="F263">
-        <v>64</v>
-      </c>
-      <c r="G263" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M64</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>16</v>
       </c>
@@ -6626,15 +4780,8 @@
       <c r="E264" t="s">
         <v>11</v>
       </c>
-      <c r="F264">
-        <v>65</v>
-      </c>
-      <c r="G264" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M65</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>16</v>
       </c>
@@ -6650,15 +4797,8 @@
       <c r="E265" t="s">
         <v>11</v>
       </c>
-      <c r="F265">
-        <v>66</v>
-      </c>
-      <c r="G265" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M66</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>16</v>
       </c>
@@ -6674,15 +4814,8 @@
       <c r="E266" t="s">
         <v>11</v>
       </c>
-      <c r="F266">
-        <v>28</v>
-      </c>
-      <c r="G266" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M28</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>16</v>
       </c>
@@ -6698,15 +4831,8 @@
       <c r="E267" t="s">
         <v>11</v>
       </c>
-      <c r="F267">
-        <v>29</v>
-      </c>
-      <c r="G267" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M29</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>16</v>
       </c>
@@ -6722,15 +4848,8 @@
       <c r="E268" t="s">
         <v>11</v>
       </c>
-      <c r="F268">
-        <v>30</v>
-      </c>
-      <c r="G268" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M30</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>16</v>
       </c>
@@ -6746,15 +4865,8 @@
       <c r="E269" t="s">
         <v>11</v>
       </c>
-      <c r="F269">
-        <v>31</v>
-      </c>
-      <c r="G269" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M31</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>16</v>
       </c>
@@ -6770,15 +4882,8 @@
       <c r="E270" t="s">
         <v>11</v>
       </c>
-      <c r="F270">
-        <v>32</v>
-      </c>
-      <c r="G270" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M32</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>16</v>
       </c>
@@ -6794,15 +4899,8 @@
       <c r="E271" t="s">
         <v>11</v>
       </c>
-      <c r="F271">
-        <v>33</v>
-      </c>
-      <c r="G271" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M33</v>
-      </c>
-    </row>
-    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>16</v>
       </c>
@@ -6818,15 +4916,8 @@
       <c r="E272" t="s">
         <v>11</v>
       </c>
-      <c r="F272">
-        <v>34</v>
-      </c>
-      <c r="G272" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M34</v>
-      </c>
-    </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>16</v>
       </c>
@@ -6839,15 +4930,8 @@
       <c r="E273" t="s">
         <v>11</v>
       </c>
-      <c r="F273">
-        <v>35</v>
-      </c>
-      <c r="G273" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M35</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="274" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>16</v>
       </c>
@@ -6860,15 +4944,8 @@
       <c r="E274" t="s">
         <v>11</v>
       </c>
-      <c r="F274">
-        <v>36</v>
-      </c>
-      <c r="G274" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M36</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>16</v>
       </c>
@@ -6884,15 +4961,8 @@
       <c r="E275" t="s">
         <v>11</v>
       </c>
-      <c r="F275">
-        <v>37</v>
-      </c>
-      <c r="G275" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M37</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="276" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>16</v>
       </c>
@@ -6908,15 +4978,8 @@
       <c r="E276" t="s">
         <v>11</v>
       </c>
-      <c r="F276">
-        <v>38</v>
-      </c>
-      <c r="G276" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M38</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>16</v>
       </c>
@@ -6932,15 +4995,8 @@
       <c r="E277" t="s">
         <v>11</v>
       </c>
-      <c r="F277">
-        <v>39</v>
-      </c>
-      <c r="G277" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M39</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>16</v>
       </c>
@@ -6956,15 +5012,8 @@
       <c r="E278" t="s">
         <v>11</v>
       </c>
-      <c r="F278">
-        <v>40</v>
-      </c>
-      <c r="G278" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M40</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>16</v>
       </c>
@@ -6980,15 +5029,8 @@
       <c r="E279" t="s">
         <v>11</v>
       </c>
-      <c r="F279">
-        <v>41</v>
-      </c>
-      <c r="G279" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M41</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>16</v>
       </c>
@@ -7001,15 +5043,8 @@
       <c r="E280" t="s">
         <v>11</v>
       </c>
-      <c r="F280">
-        <v>42</v>
-      </c>
-      <c r="G280" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M42</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="281" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
         <v>16</v>
       </c>
@@ -7022,15 +5057,8 @@
       <c r="E281" t="s">
         <v>11</v>
       </c>
-      <c r="F281">
-        <v>43</v>
-      </c>
-      <c r="G281" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M43</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>16</v>
       </c>
@@ -7043,15 +5071,8 @@
       <c r="E282" t="s">
         <v>11</v>
       </c>
-      <c r="F282">
-        <v>44</v>
-      </c>
-      <c r="G282" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M44</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>16</v>
       </c>
@@ -7064,15 +5085,8 @@
       <c r="E283" t="s">
         <v>11</v>
       </c>
-      <c r="F283">
-        <v>45</v>
-      </c>
-      <c r="G283" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M45</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>16</v>
       </c>
@@ -7088,15 +5102,8 @@
       <c r="E284" t="s">
         <v>11</v>
       </c>
-      <c r="F284">
-        <v>46</v>
-      </c>
-      <c r="G284" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M46</v>
-      </c>
-    </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>16</v>
       </c>
@@ -7112,15 +5119,8 @@
       <c r="E285" t="s">
         <v>11</v>
       </c>
-      <c r="F285">
-        <v>47</v>
-      </c>
-      <c r="G285" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M47</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>16</v>
       </c>
@@ -7136,15 +5136,8 @@
       <c r="E286" t="s">
         <v>11</v>
       </c>
-      <c r="F286">
-        <v>48</v>
-      </c>
-      <c r="G286" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M48</v>
-      </c>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="287" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
         <v>16</v>
       </c>
@@ -7160,15 +5153,8 @@
       <c r="E287" t="s">
         <v>11</v>
       </c>
-      <c r="F287">
-        <v>49</v>
-      </c>
-      <c r="G287" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M49</v>
-      </c>
-    </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>16</v>
       </c>
@@ -7184,15 +5170,8 @@
       <c r="E288" t="s">
         <v>11</v>
       </c>
-      <c r="F288">
-        <v>50</v>
-      </c>
-      <c r="G288" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M50</v>
-      </c>
-    </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>16</v>
       </c>
@@ -7208,15 +5187,8 @@
       <c r="E289" t="s">
         <v>11</v>
       </c>
-      <c r="F289">
-        <v>51</v>
-      </c>
-      <c r="G289" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M51</v>
-      </c>
-    </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>16</v>
       </c>
@@ -7232,15 +5204,8 @@
       <c r="E290" t="s">
         <v>11</v>
       </c>
-      <c r="F290">
-        <v>52</v>
-      </c>
-      <c r="G290" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M52</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="291" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>16</v>
       </c>
@@ -7256,15 +5221,8 @@
       <c r="E291" t="s">
         <v>11</v>
       </c>
-      <c r="F291">
-        <v>53</v>
-      </c>
-      <c r="G291" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M53</v>
-      </c>
-    </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>16</v>
       </c>
@@ -7280,15 +5238,8 @@
       <c r="E292" t="s">
         <v>11</v>
       </c>
-      <c r="F292">
-        <v>54</v>
-      </c>
-      <c r="G292" t="str">
-        <f t="shared" si="4"/>
-        <v>E32M54</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="293" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
         <v>17</v>
       </c>
@@ -7304,15 +5255,8 @@
       <c r="E293" t="s">
         <v>18</v>
       </c>
-      <c r="F293">
-        <v>1</v>
-      </c>
-      <c r="G293" t="str">
-        <f>_xlfn.CONCAT("E43M",F293)</f>
-        <v>E43M1</v>
-      </c>
-    </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>17</v>
       </c>
@@ -7328,15 +5272,8 @@
       <c r="E294" t="s">
         <v>18</v>
       </c>
-      <c r="F294">
-        <v>2</v>
-      </c>
-      <c r="G294" t="str">
-        <f t="shared" ref="G294:G357" si="5">_xlfn.CONCAT("E43M",F294)</f>
-        <v>E43M2</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>17</v>
       </c>
@@ -7352,15 +5289,8 @@
       <c r="E295" t="s">
         <v>18</v>
       </c>
-      <c r="F295">
-        <v>3</v>
-      </c>
-      <c r="G295" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M3</v>
-      </c>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>17</v>
       </c>
@@ -7376,15 +5306,8 @@
       <c r="E296" t="s">
         <v>18</v>
       </c>
-      <c r="F296">
-        <v>4</v>
-      </c>
-      <c r="G296" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M4</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="297" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
         <v>17</v>
       </c>
@@ -7397,15 +5320,8 @@
       <c r="E297" t="s">
         <v>18</v>
       </c>
-      <c r="F297">
-        <v>5</v>
-      </c>
-      <c r="G297" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M5</v>
-      </c>
-    </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>17</v>
       </c>
@@ -7418,15 +5334,8 @@
       <c r="E298" t="s">
         <v>18</v>
       </c>
-      <c r="F298">
-        <v>6</v>
-      </c>
-      <c r="G298" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M6</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="299" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
         <v>17</v>
       </c>
@@ -7439,15 +5348,8 @@
       <c r="E299" t="s">
         <v>18</v>
       </c>
-      <c r="F299">
-        <v>7</v>
-      </c>
-      <c r="G299" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M7</v>
-      </c>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>17</v>
       </c>
@@ -7460,15 +5362,8 @@
       <c r="E300" t="s">
         <v>18</v>
       </c>
-      <c r="F300">
-        <v>8</v>
-      </c>
-      <c r="G300" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M8</v>
-      </c>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>17</v>
       </c>
@@ -7481,15 +5376,8 @@
       <c r="E301" t="s">
         <v>18</v>
       </c>
-      <c r="F301">
-        <v>9</v>
-      </c>
-      <c r="G301" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M9</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>17</v>
       </c>
@@ -7502,15 +5390,8 @@
       <c r="E302" t="s">
         <v>18</v>
       </c>
-      <c r="F302">
-        <v>10</v>
-      </c>
-      <c r="G302" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M10</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>17</v>
       </c>
@@ -7523,15 +5404,8 @@
       <c r="E303" t="s">
         <v>18</v>
       </c>
-      <c r="F303">
-        <v>11</v>
-      </c>
-      <c r="G303" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M11</v>
-      </c>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>17</v>
       </c>
@@ -7544,15 +5418,8 @@
       <c r="E304" t="s">
         <v>18</v>
       </c>
-      <c r="F304">
-        <v>12</v>
-      </c>
-      <c r="G304" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M12</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="305" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
         <v>17</v>
       </c>
@@ -7565,15 +5432,8 @@
       <c r="E305" t="s">
         <v>18</v>
       </c>
-      <c r="F305">
-        <v>13</v>
-      </c>
-      <c r="G305" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M13</v>
-      </c>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="306" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A306" t="s">
         <v>17</v>
       </c>
@@ -7586,15 +5446,8 @@
       <c r="E306" t="s">
         <v>18</v>
       </c>
-      <c r="F306">
-        <v>14</v>
-      </c>
-      <c r="G306" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M14</v>
-      </c>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>17</v>
       </c>
@@ -7610,15 +5463,8 @@
       <c r="E307" t="s">
         <v>18</v>
       </c>
-      <c r="F307">
-        <v>15</v>
-      </c>
-      <c r="G307" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M15</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>17</v>
       </c>
@@ -7634,15 +5480,8 @@
       <c r="E308" t="s">
         <v>18</v>
       </c>
-      <c r="F308">
-        <v>16</v>
-      </c>
-      <c r="G308" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M16</v>
-      </c>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>17</v>
       </c>
@@ -7658,15 +5497,8 @@
       <c r="E309" t="s">
         <v>18</v>
       </c>
-      <c r="F309">
-        <v>17</v>
-      </c>
-      <c r="G309" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M17</v>
-      </c>
-    </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>17</v>
       </c>
@@ -7682,15 +5514,8 @@
       <c r="E310" t="s">
         <v>18</v>
       </c>
-      <c r="F310">
-        <v>18</v>
-      </c>
-      <c r="G310" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M18</v>
-      </c>
-    </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>17</v>
       </c>
@@ -7706,15 +5531,8 @@
       <c r="E311" t="s">
         <v>18</v>
       </c>
-      <c r="F311">
-        <v>19</v>
-      </c>
-      <c r="G311" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M19</v>
-      </c>
-    </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>17</v>
       </c>
@@ -7730,15 +5548,8 @@
       <c r="E312" t="s">
         <v>18</v>
       </c>
-      <c r="F312">
-        <v>20</v>
-      </c>
-      <c r="G312" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M20</v>
-      </c>
-    </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="313" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
         <v>17</v>
       </c>
@@ -7754,15 +5565,8 @@
       <c r="E313" t="s">
         <v>18</v>
       </c>
-      <c r="F313">
-        <v>21</v>
-      </c>
-      <c r="G313" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M21</v>
-      </c>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>17</v>
       </c>
@@ -7775,15 +5579,8 @@
       <c r="E314" t="s">
         <v>18</v>
       </c>
-      <c r="F314">
-        <v>22</v>
-      </c>
-      <c r="G314" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M22</v>
-      </c>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>17</v>
       </c>
@@ -7796,15 +5593,8 @@
       <c r="E315" t="s">
         <v>18</v>
       </c>
-      <c r="F315">
-        <v>23</v>
-      </c>
-      <c r="G315" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M23</v>
-      </c>
-    </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="316" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
         <v>17</v>
       </c>
@@ -7817,15 +5607,8 @@
       <c r="E316" t="s">
         <v>18</v>
       </c>
-      <c r="F316">
-        <v>24</v>
-      </c>
-      <c r="G316" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M24</v>
-      </c>
-    </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>17</v>
       </c>
@@ -7838,15 +5621,8 @@
       <c r="E317" t="s">
         <v>18</v>
       </c>
-      <c r="F317">
-        <v>25</v>
-      </c>
-      <c r="G317" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M25</v>
-      </c>
-    </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="318" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A318" t="s">
         <v>17</v>
       </c>
@@ -7859,15 +5635,8 @@
       <c r="E318" t="s">
         <v>18</v>
       </c>
-      <c r="F318">
-        <v>26</v>
-      </c>
-      <c r="G318" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M26</v>
-      </c>
-    </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>17</v>
       </c>
@@ -7880,15 +5649,8 @@
       <c r="E319" t="s">
         <v>18</v>
       </c>
-      <c r="F319">
-        <v>27</v>
-      </c>
-      <c r="G319" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M27</v>
-      </c>
-    </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="320" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A320" t="s">
         <v>17</v>
       </c>
@@ -7901,15 +5663,8 @@
       <c r="E320" t="s">
         <v>18</v>
       </c>
-      <c r="F320">
-        <v>28</v>
-      </c>
-      <c r="G320" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M28</v>
-      </c>
-    </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="321" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A321" t="s">
         <v>17</v>
       </c>
@@ -7925,15 +5680,8 @@
       <c r="E321" t="s">
         <v>18</v>
       </c>
-      <c r="F321">
-        <v>29</v>
-      </c>
-      <c r="G321" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M29</v>
-      </c>
-    </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="322" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A322" t="s">
         <v>17</v>
       </c>
@@ -7949,15 +5697,8 @@
       <c r="E322" t="s">
         <v>18</v>
       </c>
-      <c r="F322">
-        <v>30</v>
-      </c>
-      <c r="G322" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M30</v>
-      </c>
-    </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="323" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A323" t="s">
         <v>17</v>
       </c>
@@ -7973,15 +5714,8 @@
       <c r="E323" t="s">
         <v>18</v>
       </c>
-      <c r="F323">
-        <v>31</v>
-      </c>
-      <c r="G323" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M31</v>
-      </c>
-    </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>17</v>
       </c>
@@ -7997,15 +5731,8 @@
       <c r="E324" t="s">
         <v>18</v>
       </c>
-      <c r="F324">
-        <v>32</v>
-      </c>
-      <c r="G324" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M32</v>
-      </c>
-    </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="325" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A325" t="s">
         <v>17</v>
       </c>
@@ -8021,15 +5748,8 @@
       <c r="E325" t="s">
         <v>18</v>
       </c>
-      <c r="F325">
-        <v>33</v>
-      </c>
-      <c r="G325" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M33</v>
-      </c>
-    </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="326" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A326" t="s">
         <v>17</v>
       </c>
@@ -8045,15 +5765,8 @@
       <c r="E326" t="s">
         <v>18</v>
       </c>
-      <c r="F326">
-        <v>34</v>
-      </c>
-      <c r="G326" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M34</v>
-      </c>
-    </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="327" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A327" t="s">
         <v>17</v>
       </c>
@@ -8069,15 +5782,8 @@
       <c r="E327" t="s">
         <v>18</v>
       </c>
-      <c r="F327">
-        <v>35</v>
-      </c>
-      <c r="G327" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M35</v>
-      </c>
-    </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="328" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A328" t="s">
         <v>17</v>
       </c>
@@ -8093,15 +5799,8 @@
       <c r="E328" t="s">
         <v>18</v>
       </c>
-      <c r="F328">
-        <v>36</v>
-      </c>
-      <c r="G328" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M36</v>
-      </c>
-    </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="329" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A329" t="s">
         <v>17</v>
       </c>
@@ -8117,15 +5816,8 @@
       <c r="E329" t="s">
         <v>18</v>
       </c>
-      <c r="F329">
-        <v>37</v>
-      </c>
-      <c r="G329" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M37</v>
-      </c>
-    </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="330" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A330" t="s">
         <v>17</v>
       </c>
@@ -8141,15 +5833,8 @@
       <c r="E330" t="s">
         <v>18</v>
       </c>
-      <c r="F330">
-        <v>38</v>
-      </c>
-      <c r="G330" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M38</v>
-      </c>
-    </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="331" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A331" t="s">
         <v>17</v>
       </c>
@@ -8165,15 +5850,8 @@
       <c r="E331" t="s">
         <v>18</v>
       </c>
-      <c r="F331">
-        <v>39</v>
-      </c>
-      <c r="G331" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M39</v>
-      </c>
-    </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="332" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A332" t="s">
         <v>17</v>
       </c>
@@ -8189,15 +5867,8 @@
       <c r="E332" t="s">
         <v>18</v>
       </c>
-      <c r="F332">
-        <v>40</v>
-      </c>
-      <c r="G332" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M40</v>
-      </c>
-    </row>
-    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="333" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A333" t="s">
         <v>17</v>
       </c>
@@ -8213,15 +5884,8 @@
       <c r="E333" t="s">
         <v>18</v>
       </c>
-      <c r="F333">
-        <v>41</v>
-      </c>
-      <c r="G333" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M41</v>
-      </c>
-    </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="334" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A334" t="s">
         <v>17</v>
       </c>
@@ -8234,15 +5898,8 @@
       <c r="E334" t="s">
         <v>18</v>
       </c>
-      <c r="F334">
-        <v>42</v>
-      </c>
-      <c r="G334" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M42</v>
-      </c>
-    </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="335" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A335" t="s">
         <v>17</v>
       </c>
@@ -8258,15 +5915,8 @@
       <c r="E335" t="s">
         <v>18</v>
       </c>
-      <c r="F335">
-        <v>43</v>
-      </c>
-      <c r="G335" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M43</v>
-      </c>
-    </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="336" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A336" t="s">
         <v>17</v>
       </c>
@@ -8282,15 +5932,8 @@
       <c r="E336" t="s">
         <v>18</v>
       </c>
-      <c r="F336">
-        <v>44</v>
-      </c>
-      <c r="G336" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M44</v>
-      </c>
-    </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>17</v>
       </c>
@@ -8306,15 +5949,8 @@
       <c r="E337" t="s">
         <v>18</v>
       </c>
-      <c r="F337">
-        <v>45</v>
-      </c>
-      <c r="G337" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M45</v>
-      </c>
-    </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>17</v>
       </c>
@@ -8330,15 +5966,8 @@
       <c r="E338" t="s">
         <v>18</v>
       </c>
-      <c r="F338">
-        <v>46</v>
-      </c>
-      <c r="G338" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M46</v>
-      </c>
-    </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="339" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A339" t="s">
         <v>17</v>
       </c>
@@ -8354,15 +5983,8 @@
       <c r="E339" t="s">
         <v>18</v>
       </c>
-      <c r="F339">
-        <v>47</v>
-      </c>
-      <c r="G339" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M47</v>
-      </c>
-    </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="340" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A340" t="s">
         <v>17</v>
       </c>
@@ -8378,15 +6000,8 @@
       <c r="E340" t="s">
         <v>18</v>
       </c>
-      <c r="F340">
-        <v>48</v>
-      </c>
-      <c r="G340" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M48</v>
-      </c>
-    </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>17</v>
       </c>
@@ -8402,15 +6017,8 @@
       <c r="E341" t="s">
         <v>18</v>
       </c>
-      <c r="F341">
-        <v>49</v>
-      </c>
-      <c r="G341" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M49</v>
-      </c>
-    </row>
-    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="342" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A342" t="s">
         <v>17</v>
       </c>
@@ -8426,15 +6034,8 @@
       <c r="E342" t="s">
         <v>18</v>
       </c>
-      <c r="F342">
-        <v>50</v>
-      </c>
-      <c r="G342" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M50</v>
-      </c>
-    </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="343" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A343" t="s">
         <v>17</v>
       </c>
@@ -8450,15 +6051,8 @@
       <c r="E343" t="s">
         <v>18</v>
       </c>
-      <c r="F343">
-        <v>51</v>
-      </c>
-      <c r="G343" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M51</v>
-      </c>
-    </row>
-    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="344" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A344" t="s">
         <v>17</v>
       </c>
@@ -8474,15 +6068,8 @@
       <c r="E344" t="s">
         <v>18</v>
       </c>
-      <c r="F344">
-        <v>52</v>
-      </c>
-      <c r="G344" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M52</v>
-      </c>
-    </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>17</v>
       </c>
@@ -8498,15 +6085,8 @@
       <c r="E345" t="s">
         <v>18</v>
       </c>
-      <c r="F345">
-        <v>53</v>
-      </c>
-      <c r="G345" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M53</v>
-      </c>
-    </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="346" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A346" t="s">
         <v>17</v>
       </c>
@@ -8522,15 +6102,8 @@
       <c r="E346" t="s">
         <v>18</v>
       </c>
-      <c r="F346">
-        <v>54</v>
-      </c>
-      <c r="G346" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M54</v>
-      </c>
-    </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>17</v>
       </c>
@@ -8546,15 +6119,8 @@
       <c r="E347" t="s">
         <v>18</v>
       </c>
-      <c r="F347">
-        <v>55</v>
-      </c>
-      <c r="G347" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M55</v>
-      </c>
-    </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="348" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A348" t="s">
         <v>17</v>
       </c>
@@ -8570,15 +6136,8 @@
       <c r="E348" t="s">
         <v>18</v>
       </c>
-      <c r="F348">
-        <v>56</v>
-      </c>
-      <c r="G348" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M56</v>
-      </c>
-    </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="349" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A349" t="s">
         <v>17</v>
       </c>
@@ -8591,15 +6150,8 @@
       <c r="E349" t="s">
         <v>18</v>
       </c>
-      <c r="F349">
-        <v>1</v>
-      </c>
-      <c r="G349" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M1</v>
-      </c>
-    </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="350" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A350" t="s">
         <v>17</v>
       </c>
@@ -8612,15 +6164,8 @@
       <c r="E350" t="s">
         <v>18</v>
       </c>
-      <c r="F350">
-        <v>2</v>
-      </c>
-      <c r="G350" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M2</v>
-      </c>
-    </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="351" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A351" t="s">
         <v>17</v>
       </c>
@@ -8633,15 +6178,8 @@
       <c r="E351" t="s">
         <v>18</v>
       </c>
-      <c r="F351">
-        <v>3</v>
-      </c>
-      <c r="G351" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M3</v>
-      </c>
-    </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="352" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A352" t="s">
         <v>17</v>
       </c>
@@ -8654,15 +6192,8 @@
       <c r="E352" t="s">
         <v>18</v>
       </c>
-      <c r="F352">
-        <v>4</v>
-      </c>
-      <c r="G352" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M4</v>
-      </c>
-    </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="353" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A353" t="s">
         <v>17</v>
       </c>
@@ -8675,15 +6206,8 @@
       <c r="E353" t="s">
         <v>18</v>
       </c>
-      <c r="F353">
-        <v>5</v>
-      </c>
-      <c r="G353" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M5</v>
-      </c>
-    </row>
-    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="354" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A354" t="s">
         <v>17</v>
       </c>
@@ -8696,15 +6220,8 @@
       <c r="E354" t="s">
         <v>18</v>
       </c>
-      <c r="F354">
-        <v>6</v>
-      </c>
-      <c r="G354" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M6</v>
-      </c>
-    </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>17</v>
       </c>
@@ -8717,15 +6234,8 @@
       <c r="E355" t="s">
         <v>18</v>
       </c>
-      <c r="F355">
-        <v>7</v>
-      </c>
-      <c r="G355" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M7</v>
-      </c>
-    </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>17</v>
       </c>
@@ -8738,15 +6248,8 @@
       <c r="E356" t="s">
         <v>18</v>
       </c>
-      <c r="F356">
-        <v>8</v>
-      </c>
-      <c r="G356" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M8</v>
-      </c>
-    </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="357" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A357" t="s">
         <v>17</v>
       </c>
@@ -8759,15 +6262,8 @@
       <c r="E357" t="s">
         <v>18</v>
       </c>
-      <c r="F357">
-        <v>9</v>
-      </c>
-      <c r="G357" t="str">
-        <f t="shared" si="5"/>
-        <v>E43M9</v>
-      </c>
-    </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>17</v>
       </c>
@@ -8780,15 +6276,8 @@
       <c r="E358" t="s">
         <v>18</v>
       </c>
-      <c r="F358">
-        <v>10</v>
-      </c>
-      <c r="G358" t="str">
-        <f t="shared" ref="G358:G421" si="6">_xlfn.CONCAT("E43M",F358)</f>
-        <v>E43M10</v>
-      </c>
-    </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="359" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A359" t="s">
         <v>17</v>
       </c>
@@ -8801,15 +6290,8 @@
       <c r="E359" t="s">
         <v>18</v>
       </c>
-      <c r="F359">
-        <v>11</v>
-      </c>
-      <c r="G359" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M11</v>
-      </c>
-    </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="360" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A360" t="s">
         <v>17</v>
       </c>
@@ -8822,15 +6304,8 @@
       <c r="E360" t="s">
         <v>18</v>
       </c>
-      <c r="F360">
-        <v>12</v>
-      </c>
-      <c r="G360" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M12</v>
-      </c>
-    </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="361" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A361" t="s">
         <v>17</v>
       </c>
@@ -8843,15 +6318,8 @@
       <c r="E361" t="s">
         <v>18</v>
       </c>
-      <c r="F361">
-        <v>13</v>
-      </c>
-      <c r="G361" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M13</v>
-      </c>
-    </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="362" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A362" t="s">
         <v>17</v>
       </c>
@@ -8864,15 +6332,8 @@
       <c r="E362" t="s">
         <v>18</v>
       </c>
-      <c r="F362">
-        <v>14</v>
-      </c>
-      <c r="G362" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M14</v>
-      </c>
-    </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>17</v>
       </c>
@@ -8885,15 +6346,8 @@
       <c r="E363" t="s">
         <v>18</v>
       </c>
-      <c r="F363">
-        <v>15</v>
-      </c>
-      <c r="G363" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M15</v>
-      </c>
-    </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="364" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A364" t="s">
         <v>17</v>
       </c>
@@ -8906,15 +6360,8 @@
       <c r="E364" t="s">
         <v>18</v>
       </c>
-      <c r="F364">
-        <v>16</v>
-      </c>
-      <c r="G364" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M16</v>
-      </c>
-    </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="365" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A365" t="s">
         <v>17</v>
       </c>
@@ -8927,15 +6374,8 @@
       <c r="E365" t="s">
         <v>18</v>
       </c>
-      <c r="F365">
-        <v>17</v>
-      </c>
-      <c r="G365" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M17</v>
-      </c>
-    </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="366" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A366" t="s">
         <v>17</v>
       </c>
@@ -8948,15 +6388,8 @@
       <c r="E366" t="s">
         <v>18</v>
       </c>
-      <c r="F366">
-        <v>18</v>
-      </c>
-      <c r="G366" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M18</v>
-      </c>
-    </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="367" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A367" t="s">
         <v>17</v>
       </c>
@@ -8969,15 +6402,8 @@
       <c r="E367" t="s">
         <v>18</v>
       </c>
-      <c r="F367">
-        <v>19</v>
-      </c>
-      <c r="G367" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M19</v>
-      </c>
-    </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>17</v>
       </c>
@@ -8990,15 +6416,8 @@
       <c r="E368" t="s">
         <v>18</v>
       </c>
-      <c r="F368">
-        <v>20</v>
-      </c>
-      <c r="G368" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M20</v>
-      </c>
-    </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="369" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A369" t="s">
         <v>17</v>
       </c>
@@ -9011,15 +6430,8 @@
       <c r="E369" t="s">
         <v>18</v>
       </c>
-      <c r="F369">
-        <v>21</v>
-      </c>
-      <c r="G369" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M21</v>
-      </c>
-    </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="370" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A370" t="s">
         <v>17</v>
       </c>
@@ -9032,15 +6444,8 @@
       <c r="E370" t="s">
         <v>18</v>
       </c>
-      <c r="F370">
-        <v>22</v>
-      </c>
-      <c r="G370" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M22</v>
-      </c>
-    </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>17</v>
       </c>
@@ -9053,15 +6458,8 @@
       <c r="E371" t="s">
         <v>18</v>
       </c>
-      <c r="F371">
-        <v>23</v>
-      </c>
-      <c r="G371" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M23</v>
-      </c>
-    </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>17</v>
       </c>
@@ -9074,15 +6472,8 @@
       <c r="E372" t="s">
         <v>18</v>
       </c>
-      <c r="F372">
-        <v>24</v>
-      </c>
-      <c r="G372" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M24</v>
-      </c>
-    </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="373" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A373" t="s">
         <v>17</v>
       </c>
@@ -9095,15 +6486,8 @@
       <c r="E373" t="s">
         <v>18</v>
       </c>
-      <c r="F373">
-        <v>25</v>
-      </c>
-      <c r="G373" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M25</v>
-      </c>
-    </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="374" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A374" t="s">
         <v>17</v>
       </c>
@@ -9116,15 +6500,8 @@
       <c r="E374" t="s">
         <v>18</v>
       </c>
-      <c r="F374">
-        <v>26</v>
-      </c>
-      <c r="G374" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M26</v>
-      </c>
-    </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="375" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A375" t="s">
         <v>17</v>
       </c>
@@ -9137,15 +6514,8 @@
       <c r="E375" t="s">
         <v>18</v>
       </c>
-      <c r="F375">
-        <v>27</v>
-      </c>
-      <c r="G375" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M27</v>
-      </c>
-    </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="376" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A376" t="s">
         <v>17</v>
       </c>
@@ -9158,15 +6528,8 @@
       <c r="E376" t="s">
         <v>18</v>
       </c>
-      <c r="F376">
-        <v>28</v>
-      </c>
-      <c r="G376" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M28</v>
-      </c>
-    </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="377" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>17</v>
       </c>
@@ -9182,15 +6545,8 @@
       <c r="E377" t="s">
         <v>18</v>
       </c>
-      <c r="F377">
-        <v>29</v>
-      </c>
-      <c r="G377" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M29</v>
-      </c>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="378" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A378" t="s">
         <v>17</v>
       </c>
@@ -9203,15 +6559,8 @@
       <c r="E378" t="s">
         <v>18</v>
       </c>
-      <c r="F378">
-        <v>30</v>
-      </c>
-      <c r="G378" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M30</v>
-      </c>
-    </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>17</v>
       </c>
@@ -9227,15 +6576,8 @@
       <c r="E379" t="s">
         <v>18</v>
       </c>
-      <c r="F379">
-        <v>31</v>
-      </c>
-      <c r="G379" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M31</v>
-      </c>
-    </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="380" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A380" t="s">
         <v>17</v>
       </c>
@@ -9248,15 +6590,8 @@
       <c r="E380" t="s">
         <v>18</v>
       </c>
-      <c r="F380">
-        <v>32</v>
-      </c>
-      <c r="G380" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M32</v>
-      </c>
-    </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="381" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A381" t="s">
         <v>17</v>
       </c>
@@ -9269,15 +6604,8 @@
       <c r="E381" t="s">
         <v>18</v>
       </c>
-      <c r="F381">
-        <v>33</v>
-      </c>
-      <c r="G381" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M33</v>
-      </c>
-    </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="382" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A382" t="s">
         <v>17</v>
       </c>
@@ -9293,15 +6621,8 @@
       <c r="E382" t="s">
         <v>18</v>
       </c>
-      <c r="F382">
-        <v>34</v>
-      </c>
-      <c r="G382" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M34</v>
-      </c>
-    </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="383" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A383" t="s">
         <v>17</v>
       </c>
@@ -9317,15 +6638,8 @@
       <c r="E383" t="s">
         <v>18</v>
       </c>
-      <c r="F383">
-        <v>35</v>
-      </c>
-      <c r="G383" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M35</v>
-      </c>
-    </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="384" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A384" t="s">
         <v>17</v>
       </c>
@@ -9341,15 +6655,8 @@
       <c r="E384" t="s">
         <v>18</v>
       </c>
-      <c r="F384">
-        <v>36</v>
-      </c>
-      <c r="G384" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M36</v>
-      </c>
-    </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="385" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A385" t="s">
         <v>17</v>
       </c>
@@ -9362,15 +6669,8 @@
       <c r="E385" t="s">
         <v>18</v>
       </c>
-      <c r="F385">
-        <v>37</v>
-      </c>
-      <c r="G385" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M37</v>
-      </c>
-    </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>17</v>
       </c>
@@ -9386,15 +6686,8 @@
       <c r="E386" t="s">
         <v>18</v>
       </c>
-      <c r="F386">
-        <v>38</v>
-      </c>
-      <c r="G386" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M38</v>
-      </c>
-    </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="387" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A387" t="s">
         <v>17</v>
       </c>
@@ -9407,15 +6700,8 @@
       <c r="E387" t="s">
         <v>18</v>
       </c>
-      <c r="F387">
-        <v>39</v>
-      </c>
-      <c r="G387" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M39</v>
-      </c>
-    </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="388" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>17</v>
       </c>
@@ -9428,15 +6714,8 @@
       <c r="E388" t="s">
         <v>18</v>
       </c>
-      <c r="F388">
-        <v>40</v>
-      </c>
-      <c r="G388" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M40</v>
-      </c>
-    </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="389" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A389" t="s">
         <v>17</v>
       </c>
@@ -9452,15 +6731,8 @@
       <c r="E389" t="s">
         <v>18</v>
       </c>
-      <c r="F389">
-        <v>41</v>
-      </c>
-      <c r="G389" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M41</v>
-      </c>
-    </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>17</v>
       </c>
@@ -9473,15 +6745,8 @@
       <c r="E390" t="s">
         <v>18</v>
       </c>
-      <c r="F390">
-        <v>42</v>
-      </c>
-      <c r="G390" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M42</v>
-      </c>
-    </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="391" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
         <v>17</v>
       </c>
@@ -9497,15 +6762,8 @@
       <c r="E391" t="s">
         <v>18</v>
       </c>
-      <c r="F391">
-        <v>43</v>
-      </c>
-      <c r="G391" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M43</v>
-      </c>
-    </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>17</v>
       </c>
@@ -9518,15 +6776,8 @@
       <c r="E392" t="s">
         <v>18</v>
       </c>
-      <c r="F392">
-        <v>44</v>
-      </c>
-      <c r="G392" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M44</v>
-      </c>
-    </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="393" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
         <v>17</v>
       </c>
@@ -9542,15 +6793,8 @@
       <c r="E393" t="s">
         <v>18</v>
       </c>
-      <c r="F393">
-        <v>45</v>
-      </c>
-      <c r="G393" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M45</v>
-      </c>
-    </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="394" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A394" t="s">
         <v>17</v>
       </c>
@@ -9566,15 +6810,8 @@
       <c r="E394" t="s">
         <v>18</v>
       </c>
-      <c r="F394">
-        <v>46</v>
-      </c>
-      <c r="G394" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M46</v>
-      </c>
-    </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="395" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A395" t="s">
         <v>17</v>
       </c>
@@ -9590,15 +6827,8 @@
       <c r="E395" t="s">
         <v>18</v>
       </c>
-      <c r="F395">
-        <v>47</v>
-      </c>
-      <c r="G395" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M47</v>
-      </c>
-    </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>17</v>
       </c>
@@ -9614,15 +6844,8 @@
       <c r="E396" t="s">
         <v>18</v>
       </c>
-      <c r="F396">
-        <v>48</v>
-      </c>
-      <c r="G396" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M48</v>
-      </c>
-    </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="397" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A397" t="s">
         <v>17</v>
       </c>
@@ -9638,15 +6861,8 @@
       <c r="E397" t="s">
         <v>18</v>
       </c>
-      <c r="F397">
-        <v>49</v>
-      </c>
-      <c r="G397" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M49</v>
-      </c>
-    </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="398" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A398" t="s">
         <v>17</v>
       </c>
@@ -9662,15 +6878,8 @@
       <c r="E398" t="s">
         <v>18</v>
       </c>
-      <c r="F398">
-        <v>50</v>
-      </c>
-      <c r="G398" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M50</v>
-      </c>
-    </row>
-    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="399" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A399" t="s">
         <v>17</v>
       </c>
@@ -9686,15 +6895,8 @@
       <c r="E399" t="s">
         <v>18</v>
       </c>
-      <c r="F399">
-        <v>51</v>
-      </c>
-      <c r="G399" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M51</v>
-      </c>
-    </row>
-    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="400" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A400" t="s">
         <v>17</v>
       </c>
@@ -9710,15 +6912,8 @@
       <c r="E400" t="s">
         <v>18</v>
       </c>
-      <c r="F400">
-        <v>52</v>
-      </c>
-      <c r="G400" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M52</v>
-      </c>
-    </row>
-    <row r="401" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="401" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A401" t="s">
         <v>17</v>
       </c>
@@ -9734,15 +6929,8 @@
       <c r="E401" t="s">
         <v>18</v>
       </c>
-      <c r="F401">
-        <v>53</v>
-      </c>
-      <c r="G401" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M53</v>
-      </c>
-    </row>
-    <row r="402" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="402" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A402" t="s">
         <v>17</v>
       </c>
@@ -9758,15 +6946,8 @@
       <c r="E402" t="s">
         <v>18</v>
       </c>
-      <c r="F402">
-        <v>54</v>
-      </c>
-      <c r="G402" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M54</v>
-      </c>
-    </row>
-    <row r="403" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="403" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A403" t="s">
         <v>17</v>
       </c>
@@ -9782,15 +6963,8 @@
       <c r="E403" t="s">
         <v>18</v>
       </c>
-      <c r="F403">
-        <v>55</v>
-      </c>
-      <c r="G403" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M55</v>
-      </c>
-    </row>
-    <row r="404" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="404" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A404" t="s">
         <v>17</v>
       </c>
@@ -9806,15 +6980,8 @@
       <c r="E404" t="s">
         <v>18</v>
       </c>
-      <c r="F404">
-        <v>56</v>
-      </c>
-      <c r="G404" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M56</v>
-      </c>
-    </row>
-    <row r="405" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="405" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A405" t="s">
         <v>17</v>
       </c>
@@ -9830,15 +6997,8 @@
       <c r="E405" t="s">
         <v>18</v>
       </c>
-      <c r="F405">
-        <v>1</v>
-      </c>
-      <c r="G405" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M1</v>
-      </c>
-    </row>
-    <row r="406" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="406" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A406" t="s">
         <v>17</v>
       </c>
@@ -9854,15 +7014,8 @@
       <c r="E406" t="s">
         <v>18</v>
       </c>
-      <c r="F406">
-        <v>2</v>
-      </c>
-      <c r="G406" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M2</v>
-      </c>
-    </row>
-    <row r="407" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="407" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A407" t="s">
         <v>17</v>
       </c>
@@ -9878,15 +7031,8 @@
       <c r="E407" t="s">
         <v>18</v>
       </c>
-      <c r="F407">
-        <v>3</v>
-      </c>
-      <c r="G407" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M3</v>
-      </c>
-    </row>
-    <row r="408" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="408" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A408" t="s">
         <v>17</v>
       </c>
@@ -9902,15 +7048,8 @@
       <c r="E408" t="s">
         <v>18</v>
       </c>
-      <c r="F408">
-        <v>4</v>
-      </c>
-      <c r="G408" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M4</v>
-      </c>
-    </row>
-    <row r="409" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="409" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A409" t="s">
         <v>17</v>
       </c>
@@ -9926,15 +7065,8 @@
       <c r="E409" t="s">
         <v>18</v>
       </c>
-      <c r="F409">
-        <v>5</v>
-      </c>
-      <c r="G409" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M5</v>
-      </c>
-    </row>
-    <row r="410" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="410" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A410" t="s">
         <v>17</v>
       </c>
@@ -9950,15 +7082,8 @@
       <c r="E410" t="s">
         <v>18</v>
       </c>
-      <c r="F410">
-        <v>6</v>
-      </c>
-      <c r="G410" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M6</v>
-      </c>
-    </row>
-    <row r="411" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="411" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A411" t="s">
         <v>17</v>
       </c>
@@ -9974,15 +7099,8 @@
       <c r="E411" t="s">
         <v>18</v>
       </c>
-      <c r="F411">
-        <v>7</v>
-      </c>
-      <c r="G411" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M7</v>
-      </c>
-    </row>
-    <row r="412" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="412" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A412" t="s">
         <v>17</v>
       </c>
@@ -9998,15 +7116,8 @@
       <c r="E412" t="s">
         <v>18</v>
       </c>
-      <c r="F412">
-        <v>8</v>
-      </c>
-      <c r="G412" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M8</v>
-      </c>
-    </row>
-    <row r="413" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="413" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A413" t="s">
         <v>17</v>
       </c>
@@ -10022,15 +7133,8 @@
       <c r="E413" t="s">
         <v>18</v>
       </c>
-      <c r="F413">
-        <v>9</v>
-      </c>
-      <c r="G413" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M9</v>
-      </c>
-    </row>
-    <row r="414" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="414" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A414" t="s">
         <v>17</v>
       </c>
@@ -10046,15 +7150,8 @@
       <c r="E414" t="s">
         <v>18</v>
       </c>
-      <c r="F414">
-        <v>10</v>
-      </c>
-      <c r="G414" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M10</v>
-      </c>
-    </row>
-    <row r="415" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="415" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A415" t="s">
         <v>17</v>
       </c>
@@ -10070,15 +7167,8 @@
       <c r="E415" t="s">
         <v>18</v>
       </c>
-      <c r="F415">
-        <v>11</v>
-      </c>
-      <c r="G415" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M11</v>
-      </c>
-    </row>
-    <row r="416" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="416" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A416" t="s">
         <v>17</v>
       </c>
@@ -10094,15 +7184,8 @@
       <c r="E416" t="s">
         <v>18</v>
       </c>
-      <c r="F416">
-        <v>12</v>
-      </c>
-      <c r="G416" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M12</v>
-      </c>
-    </row>
-    <row r="417" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="417" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A417" t="s">
         <v>17</v>
       </c>
@@ -10115,15 +7198,8 @@
       <c r="E417" t="s">
         <v>18</v>
       </c>
-      <c r="F417">
-        <v>13</v>
-      </c>
-      <c r="G417" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M13</v>
-      </c>
-    </row>
-    <row r="418" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="418" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A418" t="s">
         <v>17</v>
       </c>
@@ -10136,15 +7212,8 @@
       <c r="E418" t="s">
         <v>18</v>
       </c>
-      <c r="F418">
-        <v>14</v>
-      </c>
-      <c r="G418" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M14</v>
-      </c>
-    </row>
-    <row r="419" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="419" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A419" t="s">
         <v>17</v>
       </c>
@@ -10157,15 +7226,8 @@
       <c r="E419" t="s">
         <v>18</v>
       </c>
-      <c r="F419">
-        <v>15</v>
-      </c>
-      <c r="G419" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M15</v>
-      </c>
-    </row>
-    <row r="420" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="420" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A420" t="s">
         <v>17</v>
       </c>
@@ -10178,15 +7240,8 @@
       <c r="E420" t="s">
         <v>18</v>
       </c>
-      <c r="F420">
-        <v>16</v>
-      </c>
-      <c r="G420" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M16</v>
-      </c>
-    </row>
-    <row r="421" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="421" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A421" t="s">
         <v>17</v>
       </c>
@@ -10199,15 +7254,8 @@
       <c r="E421" t="s">
         <v>18</v>
       </c>
-      <c r="F421">
-        <v>17</v>
-      </c>
-      <c r="G421" t="str">
-        <f t="shared" si="6"/>
-        <v>E43M17</v>
-      </c>
-    </row>
-    <row r="422" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="422" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A422" t="s">
         <v>17</v>
       </c>
@@ -10220,15 +7268,8 @@
       <c r="E422" t="s">
         <v>18</v>
       </c>
-      <c r="F422">
-        <v>18</v>
-      </c>
-      <c r="G422" t="str">
-        <f t="shared" ref="G422:G485" si="7">_xlfn.CONCAT("E43M",F422)</f>
-        <v>E43M18</v>
-      </c>
-    </row>
-    <row r="423" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="423" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A423" t="s">
         <v>17</v>
       </c>
@@ -10241,15 +7282,8 @@
       <c r="E423" t="s">
         <v>18</v>
       </c>
-      <c r="F423">
-        <v>19</v>
-      </c>
-      <c r="G423" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M19</v>
-      </c>
-    </row>
-    <row r="424" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="424" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A424" t="s">
         <v>17</v>
       </c>
@@ -10262,15 +7296,8 @@
       <c r="E424" t="s">
         <v>18</v>
       </c>
-      <c r="F424">
-        <v>20</v>
-      </c>
-      <c r="G424" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M20</v>
-      </c>
-    </row>
-    <row r="425" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="425" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A425" t="s">
         <v>17</v>
       </c>
@@ -10283,15 +7310,8 @@
       <c r="E425" t="s">
         <v>18</v>
       </c>
-      <c r="F425">
-        <v>21</v>
-      </c>
-      <c r="G425" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M21</v>
-      </c>
-    </row>
-    <row r="426" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="426" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A426" t="s">
         <v>17</v>
       </c>
@@ -10304,15 +7324,8 @@
       <c r="E426" t="s">
         <v>18</v>
       </c>
-      <c r="F426">
-        <v>22</v>
-      </c>
-      <c r="G426" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M22</v>
-      </c>
-    </row>
-    <row r="427" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="427" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A427" t="s">
         <v>17</v>
       </c>
@@ -10325,15 +7338,8 @@
       <c r="E427" t="s">
         <v>18</v>
       </c>
-      <c r="F427">
-        <v>23</v>
-      </c>
-      <c r="G427" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M23</v>
-      </c>
-    </row>
-    <row r="428" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="428" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A428" t="s">
         <v>17</v>
       </c>
@@ -10346,15 +7352,8 @@
       <c r="E428" t="s">
         <v>18</v>
       </c>
-      <c r="F428">
-        <v>24</v>
-      </c>
-      <c r="G428" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M24</v>
-      </c>
-    </row>
-    <row r="429" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="429" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A429" t="s">
         <v>17</v>
       </c>
@@ -10367,15 +7366,8 @@
       <c r="E429" t="s">
         <v>18</v>
       </c>
-      <c r="F429">
-        <v>25</v>
-      </c>
-      <c r="G429" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M25</v>
-      </c>
-    </row>
-    <row r="430" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="430" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A430" t="s">
         <v>17</v>
       </c>
@@ -10388,15 +7380,8 @@
       <c r="E430" t="s">
         <v>18</v>
       </c>
-      <c r="F430">
-        <v>26</v>
-      </c>
-      <c r="G430" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M26</v>
-      </c>
-    </row>
-    <row r="431" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="431" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A431" t="s">
         <v>17</v>
       </c>
@@ -10409,15 +7394,8 @@
       <c r="E431" t="s">
         <v>18</v>
       </c>
-      <c r="F431">
-        <v>27</v>
-      </c>
-      <c r="G431" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M27</v>
-      </c>
-    </row>
-    <row r="432" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="432" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A432" t="s">
         <v>17</v>
       </c>
@@ -10430,15 +7408,8 @@
       <c r="E432" t="s">
         <v>18</v>
       </c>
-      <c r="F432">
-        <v>28</v>
-      </c>
-      <c r="G432" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M28</v>
-      </c>
-    </row>
-    <row r="433" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="433" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A433" t="s">
         <v>17</v>
       </c>
@@ -10454,15 +7425,8 @@
       <c r="E433" t="s">
         <v>18</v>
       </c>
-      <c r="F433">
-        <v>29</v>
-      </c>
-      <c r="G433" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M29</v>
-      </c>
-    </row>
-    <row r="434" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="434" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A434" t="s">
         <v>17</v>
       </c>
@@ -10475,15 +7439,8 @@
       <c r="E434" t="s">
         <v>18</v>
       </c>
-      <c r="F434">
-        <v>30</v>
-      </c>
-      <c r="G434" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M30</v>
-      </c>
-    </row>
-    <row r="435" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="435" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A435" t="s">
         <v>17</v>
       </c>
@@ -10496,15 +7453,8 @@
       <c r="E435" t="s">
         <v>18</v>
       </c>
-      <c r="F435">
-        <v>31</v>
-      </c>
-      <c r="G435" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M31</v>
-      </c>
-    </row>
-    <row r="436" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="436" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A436" t="s">
         <v>17</v>
       </c>
@@ -10517,15 +7467,8 @@
       <c r="E436" t="s">
         <v>18</v>
       </c>
-      <c r="F436">
-        <v>32</v>
-      </c>
-      <c r="G436" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M32</v>
-      </c>
-    </row>
-    <row r="437" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="437" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A437" t="s">
         <v>17</v>
       </c>
@@ -10538,15 +7481,8 @@
       <c r="E437" t="s">
         <v>18</v>
       </c>
-      <c r="F437">
-        <v>33</v>
-      </c>
-      <c r="G437" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M33</v>
-      </c>
-    </row>
-    <row r="438" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="438" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A438" t="s">
         <v>17</v>
       </c>
@@ -10562,15 +7498,8 @@
       <c r="E438" t="s">
         <v>18</v>
       </c>
-      <c r="F438">
-        <v>34</v>
-      </c>
-      <c r="G438" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M34</v>
-      </c>
-    </row>
-    <row r="439" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="439" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A439" t="s">
         <v>17</v>
       </c>
@@ -10586,15 +7515,8 @@
       <c r="E439" t="s">
         <v>18</v>
       </c>
-      <c r="F439">
-        <v>35</v>
-      </c>
-      <c r="G439" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M35</v>
-      </c>
-    </row>
-    <row r="440" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="440" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A440" t="s">
         <v>17</v>
       </c>
@@ -10607,15 +7529,8 @@
       <c r="E440" t="s">
         <v>18</v>
       </c>
-      <c r="F440">
-        <v>36</v>
-      </c>
-      <c r="G440" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M36</v>
-      </c>
-    </row>
-    <row r="441" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="441" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A441" t="s">
         <v>17</v>
       </c>
@@ -10628,15 +7543,8 @@
       <c r="E441" t="s">
         <v>18</v>
       </c>
-      <c r="F441">
-        <v>37</v>
-      </c>
-      <c r="G441" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M37</v>
-      </c>
-    </row>
-    <row r="442" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="442" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A442" t="s">
         <v>17</v>
       </c>
@@ -10649,15 +7557,8 @@
       <c r="E442" t="s">
         <v>18</v>
       </c>
-      <c r="F442">
-        <v>38</v>
-      </c>
-      <c r="G442" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M38</v>
-      </c>
-    </row>
-    <row r="443" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="443" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A443" t="s">
         <v>17</v>
       </c>
@@ -10670,15 +7571,8 @@
       <c r="E443" t="s">
         <v>18</v>
       </c>
-      <c r="F443">
-        <v>39</v>
-      </c>
-      <c r="G443" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M39</v>
-      </c>
-    </row>
-    <row r="444" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="444" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A444" t="s">
         <v>17</v>
       </c>
@@ -10691,15 +7585,8 @@
       <c r="E444" t="s">
         <v>18</v>
       </c>
-      <c r="F444">
-        <v>40</v>
-      </c>
-      <c r="G444" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M40</v>
-      </c>
-    </row>
-    <row r="445" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="445" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A445" t="s">
         <v>17</v>
       </c>
@@ -10712,15 +7599,8 @@
       <c r="E445" t="s">
         <v>18</v>
       </c>
-      <c r="F445">
-        <v>41</v>
-      </c>
-      <c r="G445" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M41</v>
-      </c>
-    </row>
-    <row r="446" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="446" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A446" t="s">
         <v>17</v>
       </c>
@@ -10733,15 +7613,8 @@
       <c r="E446" t="s">
         <v>18</v>
       </c>
-      <c r="F446">
-        <v>42</v>
-      </c>
-      <c r="G446" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M42</v>
-      </c>
-    </row>
-    <row r="447" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="447" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A447" t="s">
         <v>17</v>
       </c>
@@ -10754,15 +7627,8 @@
       <c r="E447" t="s">
         <v>18</v>
       </c>
-      <c r="F447">
-        <v>43</v>
-      </c>
-      <c r="G447" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M43</v>
-      </c>
-    </row>
-    <row r="448" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="448" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A448" t="s">
         <v>17</v>
       </c>
@@ -10775,15 +7641,8 @@
       <c r="E448" t="s">
         <v>18</v>
       </c>
-      <c r="F448">
-        <v>44</v>
-      </c>
-      <c r="G448" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M44</v>
-      </c>
-    </row>
-    <row r="449" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="449" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A449" t="s">
         <v>17</v>
       </c>
@@ -10799,15 +7658,8 @@
       <c r="E449" t="s">
         <v>18</v>
       </c>
-      <c r="F449">
-        <v>45</v>
-      </c>
-      <c r="G449" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M45</v>
-      </c>
-    </row>
-    <row r="450" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="450" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A450" t="s">
         <v>17</v>
       </c>
@@ -10823,15 +7675,8 @@
       <c r="E450" t="s">
         <v>18</v>
       </c>
-      <c r="F450">
-        <v>46</v>
-      </c>
-      <c r="G450" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M46</v>
-      </c>
-    </row>
-    <row r="451" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="451" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A451" t="s">
         <v>17</v>
       </c>
@@ -10844,15 +7689,8 @@
       <c r="E451" t="s">
         <v>18</v>
       </c>
-      <c r="F451">
-        <v>47</v>
-      </c>
-      <c r="G451" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M47</v>
-      </c>
-    </row>
-    <row r="452" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="452" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A452" t="s">
         <v>17</v>
       </c>
@@ -10868,15 +7706,8 @@
       <c r="E452" t="s">
         <v>18</v>
       </c>
-      <c r="F452">
-        <v>48</v>
-      </c>
-      <c r="G452" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M48</v>
-      </c>
-    </row>
-    <row r="453" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="453" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A453" t="s">
         <v>17</v>
       </c>
@@ -10892,15 +7723,8 @@
       <c r="E453" t="s">
         <v>18</v>
       </c>
-      <c r="F453">
-        <v>49</v>
-      </c>
-      <c r="G453" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M49</v>
-      </c>
-    </row>
-    <row r="454" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="454" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A454" t="s">
         <v>17</v>
       </c>
@@ -10916,15 +7740,8 @@
       <c r="E454" t="s">
         <v>18</v>
       </c>
-      <c r="F454">
-        <v>50</v>
-      </c>
-      <c r="G454" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M50</v>
-      </c>
-    </row>
-    <row r="455" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="455" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A455" t="s">
         <v>17</v>
       </c>
@@ -10940,15 +7757,8 @@
       <c r="E455" t="s">
         <v>18</v>
       </c>
-      <c r="F455">
-        <v>51</v>
-      </c>
-      <c r="G455" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M51</v>
-      </c>
-    </row>
-    <row r="456" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="456" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A456" t="s">
         <v>17</v>
       </c>
@@ -10961,15 +7771,8 @@
       <c r="E456" t="s">
         <v>18</v>
       </c>
-      <c r="F456">
-        <v>52</v>
-      </c>
-      <c r="G456" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M52</v>
-      </c>
-    </row>
-    <row r="457" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="457" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A457" t="s">
         <v>17</v>
       </c>
@@ -10985,15 +7788,8 @@
       <c r="E457" t="s">
         <v>18</v>
       </c>
-      <c r="F457">
-        <v>53</v>
-      </c>
-      <c r="G457" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M53</v>
-      </c>
-    </row>
-    <row r="458" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="458" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A458" t="s">
         <v>17</v>
       </c>
@@ -11009,15 +7805,8 @@
       <c r="E458" t="s">
         <v>18</v>
       </c>
-      <c r="F458">
-        <v>54</v>
-      </c>
-      <c r="G458" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M54</v>
-      </c>
-    </row>
-    <row r="459" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="459" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A459" t="s">
         <v>17</v>
       </c>
@@ -11033,15 +7822,8 @@
       <c r="E459" t="s">
         <v>18</v>
       </c>
-      <c r="F459">
-        <v>55</v>
-      </c>
-      <c r="G459" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M55</v>
-      </c>
-    </row>
-    <row r="460" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="460" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A460" t="s">
         <v>17</v>
       </c>
@@ -11057,15 +7839,8 @@
       <c r="E460" t="s">
         <v>18</v>
       </c>
-      <c r="F460">
-        <v>56</v>
-      </c>
-      <c r="G460" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M56</v>
-      </c>
-    </row>
-    <row r="461" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="461" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A461" t="s">
         <v>17</v>
       </c>
@@ -11081,15 +7856,8 @@
       <c r="E461" t="s">
         <v>11</v>
       </c>
-      <c r="F461">
-        <v>1</v>
-      </c>
-      <c r="G461" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M1</v>
-      </c>
-    </row>
-    <row r="462" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="462" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A462" t="s">
         <v>17</v>
       </c>
@@ -11105,15 +7873,8 @@
       <c r="E462" t="s">
         <v>11</v>
       </c>
-      <c r="F462">
-        <v>2</v>
-      </c>
-      <c r="G462" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M2</v>
-      </c>
-    </row>
-    <row r="463" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="463" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A463" t="s">
         <v>17</v>
       </c>
@@ -11129,15 +7890,8 @@
       <c r="E463" t="s">
         <v>11</v>
       </c>
-      <c r="F463">
-        <v>3</v>
-      </c>
-      <c r="G463" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M3</v>
-      </c>
-    </row>
-    <row r="464" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="464" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A464" t="s">
         <v>17</v>
       </c>
@@ -11153,15 +7907,8 @@
       <c r="E464" t="s">
         <v>11</v>
       </c>
-      <c r="F464">
-        <v>4</v>
-      </c>
-      <c r="G464" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M4</v>
-      </c>
-    </row>
-    <row r="465" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="465" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A465" t="s">
         <v>17</v>
       </c>
@@ -11177,15 +7924,8 @@
       <c r="E465" t="s">
         <v>11</v>
       </c>
-      <c r="F465">
-        <v>5</v>
-      </c>
-      <c r="G465" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M5</v>
-      </c>
-    </row>
-    <row r="466" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="466" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A466" t="s">
         <v>17</v>
       </c>
@@ -11201,15 +7941,8 @@
       <c r="E466" t="s">
         <v>11</v>
       </c>
-      <c r="F466">
-        <v>6</v>
-      </c>
-      <c r="G466" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M6</v>
-      </c>
-    </row>
-    <row r="467" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="467" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A467" t="s">
         <v>17</v>
       </c>
@@ -11225,15 +7958,8 @@
       <c r="E467" t="s">
         <v>11</v>
       </c>
-      <c r="F467">
-        <v>7</v>
-      </c>
-      <c r="G467" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M7</v>
-      </c>
-    </row>
-    <row r="468" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="468" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A468" t="s">
         <v>17</v>
       </c>
@@ -11249,15 +7975,8 @@
       <c r="E468" t="s">
         <v>11</v>
       </c>
-      <c r="F468">
-        <v>8</v>
-      </c>
-      <c r="G468" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M8</v>
-      </c>
-    </row>
-    <row r="469" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="469" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A469" t="s">
         <v>17</v>
       </c>
@@ -11273,15 +7992,8 @@
       <c r="E469" t="s">
         <v>11</v>
       </c>
-      <c r="F469">
-        <v>9</v>
-      </c>
-      <c r="G469" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M9</v>
-      </c>
-    </row>
-    <row r="470" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="470" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A470" t="s">
         <v>17</v>
       </c>
@@ -11297,15 +8009,8 @@
       <c r="E470" t="s">
         <v>11</v>
       </c>
-      <c r="F470">
-        <v>10</v>
-      </c>
-      <c r="G470" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M10</v>
-      </c>
-    </row>
-    <row r="471" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="471" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A471" t="s">
         <v>17</v>
       </c>
@@ -11321,15 +8026,8 @@
       <c r="E471" t="s">
         <v>11</v>
       </c>
-      <c r="F471">
-        <v>11</v>
-      </c>
-      <c r="G471" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M11</v>
-      </c>
-    </row>
-    <row r="472" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="472" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A472" t="s">
         <v>17</v>
       </c>
@@ -11345,15 +8043,8 @@
       <c r="E472" t="s">
         <v>11</v>
       </c>
-      <c r="F472">
-        <v>12</v>
-      </c>
-      <c r="G472" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M12</v>
-      </c>
-    </row>
-    <row r="473" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="473" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A473" t="s">
         <v>17</v>
       </c>
@@ -11366,15 +8057,8 @@
       <c r="E473" t="s">
         <v>11</v>
       </c>
-      <c r="F473">
-        <v>13</v>
-      </c>
-      <c r="G473" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M13</v>
-      </c>
-    </row>
-    <row r="474" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="474" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A474" t="s">
         <v>17</v>
       </c>
@@ -11387,15 +8071,8 @@
       <c r="E474" t="s">
         <v>11</v>
       </c>
-      <c r="F474">
-        <v>14</v>
-      </c>
-      <c r="G474" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M14</v>
-      </c>
-    </row>
-    <row r="475" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="475" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A475" t="s">
         <v>17</v>
       </c>
@@ -11408,15 +8085,8 @@
       <c r="E475" t="s">
         <v>11</v>
       </c>
-      <c r="F475">
-        <v>15</v>
-      </c>
-      <c r="G475" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M15</v>
-      </c>
-    </row>
-    <row r="476" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="476" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A476" t="s">
         <v>17</v>
       </c>
@@ -11429,15 +8099,8 @@
       <c r="E476" t="s">
         <v>11</v>
       </c>
-      <c r="F476">
-        <v>16</v>
-      </c>
-      <c r="G476" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M16</v>
-      </c>
-    </row>
-    <row r="477" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="477" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A477" t="s">
         <v>17</v>
       </c>
@@ -11450,15 +8113,8 @@
       <c r="E477" t="s">
         <v>11</v>
       </c>
-      <c r="F477">
-        <v>17</v>
-      </c>
-      <c r="G477" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M17</v>
-      </c>
-    </row>
-    <row r="478" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="478" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A478" t="s">
         <v>17</v>
       </c>
@@ -11471,15 +8127,8 @@
       <c r="E478" t="s">
         <v>11</v>
       </c>
-      <c r="F478">
-        <v>18</v>
-      </c>
-      <c r="G478" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M18</v>
-      </c>
-    </row>
-    <row r="479" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="479" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A479" t="s">
         <v>17</v>
       </c>
@@ -11492,15 +8141,8 @@
       <c r="E479" t="s">
         <v>11</v>
       </c>
-      <c r="F479">
-        <v>19</v>
-      </c>
-      <c r="G479" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M19</v>
-      </c>
-    </row>
-    <row r="480" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="480" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A480" t="s">
         <v>17</v>
       </c>
@@ -11513,15 +8155,8 @@
       <c r="E480" t="s">
         <v>11</v>
       </c>
-      <c r="F480">
-        <v>20</v>
-      </c>
-      <c r="G480" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M20</v>
-      </c>
-    </row>
-    <row r="481" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="481" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A481" t="s">
         <v>17</v>
       </c>
@@ -11534,15 +8169,8 @@
       <c r="E481" t="s">
         <v>11</v>
       </c>
-      <c r="F481">
-        <v>21</v>
-      </c>
-      <c r="G481" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M21</v>
-      </c>
-    </row>
-    <row r="482" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="482" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A482" t="s">
         <v>17</v>
       </c>
@@ -11555,15 +8183,8 @@
       <c r="E482" t="s">
         <v>11</v>
       </c>
-      <c r="F482">
-        <v>22</v>
-      </c>
-      <c r="G482" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M22</v>
-      </c>
-    </row>
-    <row r="483" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="483" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A483" t="s">
         <v>17</v>
       </c>
@@ -11576,15 +8197,8 @@
       <c r="E483" t="s">
         <v>11</v>
       </c>
-      <c r="F483">
-        <v>23</v>
-      </c>
-      <c r="G483" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M23</v>
-      </c>
-    </row>
-    <row r="484" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="484" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A484" t="s">
         <v>17</v>
       </c>
@@ -11597,15 +8211,8 @@
       <c r="E484" t="s">
         <v>11</v>
       </c>
-      <c r="F484">
-        <v>24</v>
-      </c>
-      <c r="G484" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M24</v>
-      </c>
-    </row>
-    <row r="485" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="485" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A485" t="s">
         <v>17</v>
       </c>
@@ -11618,15 +8225,8 @@
       <c r="E485" t="s">
         <v>11</v>
       </c>
-      <c r="F485">
-        <v>25</v>
-      </c>
-      <c r="G485" t="str">
-        <f t="shared" si="7"/>
-        <v>E43M25</v>
-      </c>
-    </row>
-    <row r="486" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="486" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A486" t="s">
         <v>17</v>
       </c>
@@ -11639,15 +8239,8 @@
       <c r="E486" t="s">
         <v>11</v>
       </c>
-      <c r="F486">
-        <v>26</v>
-      </c>
-      <c r="G486" t="str">
-        <f t="shared" ref="G486:G516" si="8">_xlfn.CONCAT("E43M",F486)</f>
-        <v>E43M26</v>
-      </c>
-    </row>
-    <row r="487" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="487" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A487" t="s">
         <v>17</v>
       </c>
@@ -11660,15 +8253,8 @@
       <c r="E487" t="s">
         <v>11</v>
       </c>
-      <c r="F487">
-        <v>27</v>
-      </c>
-      <c r="G487" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M27</v>
-      </c>
-    </row>
-    <row r="488" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="488" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A488" t="s">
         <v>17</v>
       </c>
@@ -11681,15 +8267,8 @@
       <c r="E488" t="s">
         <v>11</v>
       </c>
-      <c r="F488">
-        <v>28</v>
-      </c>
-      <c r="G488" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M28</v>
-      </c>
-    </row>
-    <row r="489" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="489" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A489" t="s">
         <v>17</v>
       </c>
@@ -11705,15 +8284,8 @@
       <c r="E489" t="s">
         <v>11</v>
       </c>
-      <c r="F489">
-        <v>29</v>
-      </c>
-      <c r="G489" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M29</v>
-      </c>
-    </row>
-    <row r="490" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="490" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A490" t="s">
         <v>17</v>
       </c>
@@ -11726,15 +8298,8 @@
       <c r="E490" t="s">
         <v>11</v>
       </c>
-      <c r="F490">
-        <v>30</v>
-      </c>
-      <c r="G490" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M30</v>
-      </c>
-    </row>
-    <row r="491" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="491" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A491" t="s">
         <v>17</v>
       </c>
@@ -11747,15 +8312,8 @@
       <c r="E491" t="s">
         <v>11</v>
       </c>
-      <c r="F491">
-        <v>31</v>
-      </c>
-      <c r="G491" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M31</v>
-      </c>
-    </row>
-    <row r="492" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="492" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A492" t="s">
         <v>17</v>
       </c>
@@ -11768,15 +8326,8 @@
       <c r="E492" t="s">
         <v>11</v>
       </c>
-      <c r="F492">
-        <v>32</v>
-      </c>
-      <c r="G492" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M32</v>
-      </c>
-    </row>
-    <row r="493" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="493" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A493" t="s">
         <v>17</v>
       </c>
@@ -11789,15 +8340,8 @@
       <c r="E493" t="s">
         <v>11</v>
       </c>
-      <c r="F493">
-        <v>33</v>
-      </c>
-      <c r="G493" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M33</v>
-      </c>
-    </row>
-    <row r="494" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="494" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A494" t="s">
         <v>17</v>
       </c>
@@ -11813,15 +8357,8 @@
       <c r="E494" t="s">
         <v>11</v>
       </c>
-      <c r="F494">
-        <v>34</v>
-      </c>
-      <c r="G494" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M34</v>
-      </c>
-    </row>
-    <row r="495" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="495" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A495" t="s">
         <v>17</v>
       </c>
@@ -11837,15 +8374,8 @@
       <c r="E495" t="s">
         <v>11</v>
       </c>
-      <c r="F495">
-        <v>35</v>
-      </c>
-      <c r="G495" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M35</v>
-      </c>
-    </row>
-    <row r="496" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="496" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A496" t="s">
         <v>17</v>
       </c>
@@ -11858,15 +8388,8 @@
       <c r="E496" t="s">
         <v>11</v>
       </c>
-      <c r="F496">
-        <v>36</v>
-      </c>
-      <c r="G496" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M36</v>
-      </c>
-    </row>
-    <row r="497" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="497" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A497" t="s">
         <v>17</v>
       </c>
@@ -11879,15 +8402,8 @@
       <c r="E497" t="s">
         <v>11</v>
       </c>
-      <c r="F497">
-        <v>37</v>
-      </c>
-      <c r="G497" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M37</v>
-      </c>
-    </row>
-    <row r="498" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="498" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A498" t="s">
         <v>17</v>
       </c>
@@ -11900,15 +8416,8 @@
       <c r="E498" t="s">
         <v>11</v>
       </c>
-      <c r="F498">
-        <v>38</v>
-      </c>
-      <c r="G498" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M38</v>
-      </c>
-    </row>
-    <row r="499" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="499" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A499" t="s">
         <v>17</v>
       </c>
@@ -11921,15 +8430,8 @@
       <c r="E499" t="s">
         <v>11</v>
       </c>
-      <c r="F499">
-        <v>39</v>
-      </c>
-      <c r="G499" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M39</v>
-      </c>
-    </row>
-    <row r="500" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="500" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A500" t="s">
         <v>17</v>
       </c>
@@ -11942,15 +8444,8 @@
       <c r="E500" t="s">
         <v>11</v>
       </c>
-      <c r="F500">
-        <v>40</v>
-      </c>
-      <c r="G500" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M40</v>
-      </c>
-    </row>
-    <row r="501" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="501" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A501" t="s">
         <v>17</v>
       </c>
@@ -11963,15 +8458,8 @@
       <c r="E501" t="s">
         <v>11</v>
       </c>
-      <c r="F501">
-        <v>41</v>
-      </c>
-      <c r="G501" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M41</v>
-      </c>
-    </row>
-    <row r="502" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="502" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A502" t="s">
         <v>17</v>
       </c>
@@ -11984,15 +8472,8 @@
       <c r="E502" t="s">
         <v>11</v>
       </c>
-      <c r="F502">
-        <v>42</v>
-      </c>
-      <c r="G502" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M42</v>
-      </c>
-    </row>
-    <row r="503" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="503" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A503" t="s">
         <v>17</v>
       </c>
@@ -12005,15 +8486,8 @@
       <c r="E503" t="s">
         <v>11</v>
       </c>
-      <c r="F503">
-        <v>43</v>
-      </c>
-      <c r="G503" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M43</v>
-      </c>
-    </row>
-    <row r="504" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="504" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A504" t="s">
         <v>17</v>
       </c>
@@ -12026,15 +8500,8 @@
       <c r="E504" t="s">
         <v>11</v>
       </c>
-      <c r="F504">
-        <v>44</v>
-      </c>
-      <c r="G504" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M44</v>
-      </c>
-    </row>
-    <row r="505" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="505" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A505" t="s">
         <v>17</v>
       </c>
@@ -12050,15 +8517,8 @@
       <c r="E505" t="s">
         <v>11</v>
       </c>
-      <c r="F505">
-        <v>45</v>
-      </c>
-      <c r="G505" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M45</v>
-      </c>
-    </row>
-    <row r="506" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="506" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A506" t="s">
         <v>17</v>
       </c>
@@ -12074,15 +8534,8 @@
       <c r="E506" t="s">
         <v>11</v>
       </c>
-      <c r="F506">
-        <v>46</v>
-      </c>
-      <c r="G506" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M46</v>
-      </c>
-    </row>
-    <row r="507" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="507" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A507" t="s">
         <v>17</v>
       </c>
@@ -12095,15 +8548,8 @@
       <c r="E507" t="s">
         <v>11</v>
       </c>
-      <c r="F507">
-        <v>47</v>
-      </c>
-      <c r="G507" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M47</v>
-      </c>
-    </row>
-    <row r="508" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="508" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A508" t="s">
         <v>17</v>
       </c>
@@ -12119,15 +8565,8 @@
       <c r="E508" t="s">
         <v>11</v>
       </c>
-      <c r="F508">
-        <v>48</v>
-      </c>
-      <c r="G508" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M48</v>
-      </c>
-    </row>
-    <row r="509" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="509" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A509" t="s">
         <v>17</v>
       </c>
@@ -12143,15 +8582,8 @@
       <c r="E509" t="s">
         <v>11</v>
       </c>
-      <c r="F509">
-        <v>49</v>
-      </c>
-      <c r="G509" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M49</v>
-      </c>
-    </row>
-    <row r="510" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="510" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A510" t="s">
         <v>17</v>
       </c>
@@ -12167,15 +8599,8 @@
       <c r="E510" t="s">
         <v>11</v>
       </c>
-      <c r="F510">
-        <v>50</v>
-      </c>
-      <c r="G510" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M50</v>
-      </c>
-    </row>
-    <row r="511" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="511" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A511" t="s">
         <v>17</v>
       </c>
@@ -12191,15 +8616,8 @@
       <c r="E511" t="s">
         <v>11</v>
       </c>
-      <c r="F511">
-        <v>51</v>
-      </c>
-      <c r="G511" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M51</v>
-      </c>
-    </row>
-    <row r="512" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="512" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A512" t="s">
         <v>17</v>
       </c>
@@ -12212,15 +8630,8 @@
       <c r="E512" t="s">
         <v>11</v>
       </c>
-      <c r="F512">
-        <v>52</v>
-      </c>
-      <c r="G512" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M52</v>
-      </c>
-    </row>
-    <row r="513" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="513" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A513" t="s">
         <v>17</v>
       </c>
@@ -12236,15 +8647,8 @@
       <c r="E513" t="s">
         <v>11</v>
       </c>
-      <c r="F513">
-        <v>53</v>
-      </c>
-      <c r="G513" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M53</v>
-      </c>
-    </row>
-    <row r="514" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="514" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A514" t="s">
         <v>17</v>
       </c>
@@ -12260,15 +8664,8 @@
       <c r="E514" t="s">
         <v>11</v>
       </c>
-      <c r="F514">
-        <v>54</v>
-      </c>
-      <c r="G514" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M54</v>
-      </c>
-    </row>
-    <row r="515" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="515" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A515" t="s">
         <v>17</v>
       </c>
@@ -12284,15 +8681,8 @@
       <c r="E515" t="s">
         <v>11</v>
       </c>
-      <c r="F515">
-        <v>55</v>
-      </c>
-      <c r="G515" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M55</v>
-      </c>
-    </row>
-    <row r="516" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="516" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A516" t="s">
         <v>17</v>
       </c>
@@ -12307,13 +8697,6 @@
       </c>
       <c r="E516" t="s">
         <v>11</v>
-      </c>
-      <c r="F516">
-        <v>56</v>
-      </c>
-      <c r="G516" t="str">
-        <f t="shared" si="8"/>
-        <v>E43M56</v>
       </c>
     </row>
   </sheetData>
